--- a/products_import.xlsx
+++ b/products_import.xlsx
@@ -509,11 +509,7 @@
           <t>Eyelashes - Cluster Lasher</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Eyelashes</t>
-        </is>
-      </c>
+      <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="3" t="n">
         <v>100</v>
       </c>
@@ -528,11 +524,7 @@
           <t>Eyelashes - Striper Lashes</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Eyelashes</t>
-        </is>
-      </c>
+      <c r="B3" s="4" t="inlineStr"/>
       <c r="C3" s="5" t="n">
         <v>50</v>
       </c>
@@ -547,11 +539,7 @@
           <t>Eyelashes - Striper Small Lashes</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Eyelashes</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
       <c r="C4" s="3" t="n">
         <v>30</v>
       </c>
@@ -566,11 +554,7 @@
           <t>Foundation - Green Tea</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Foundations</t>
-        </is>
-      </c>
+      <c r="B5" s="4" t="inlineStr"/>
       <c r="C5" s="5" t="n">
         <v>70</v>
       </c>
@@ -585,11 +569,7 @@
           <t>Foundation - Sleek</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Foundations</t>
-        </is>
-      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="3" t="n">
         <v>50</v>
       </c>
@@ -604,11 +584,7 @@
           <t>Foundation - Blackopal</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Foundations</t>
-        </is>
-      </c>
+      <c r="B7" s="4" t="inlineStr"/>
       <c r="C7" s="5" t="n">
         <v>60</v>
       </c>
@@ -623,11 +599,7 @@
           <t>Primers</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Face</t>
-        </is>
-      </c>
+      <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="3" t="n">
         <v>60</v>
       </c>
@@ -642,11 +614,7 @@
           <t>Concealors</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Face</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="inlineStr"/>
       <c r="C9" s="5" t="n">
         <v>70</v>
       </c>
@@ -661,11 +629,7 @@
           <t>Liquid Matte Lipsticks</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="3" t="n">
         <v>20</v>
       </c>
@@ -680,11 +644,7 @@
           <t>Irene Lipstick</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B11" s="4" t="inlineStr"/>
       <c r="C11" s="5" t="n">
         <v>60</v>
       </c>
@@ -699,11 +659,7 @@
           <t>Normal Matte Lipstick</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="3" t="n">
         <v>200</v>
       </c>
@@ -718,11 +674,7 @@
           <t>Vaseline Lipbalm</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B13" s="4" t="inlineStr"/>
       <c r="C13" s="5" t="n">
         <v>35</v>
       </c>
@@ -737,11 +689,7 @@
           <t>Roll-on Lipbalm</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="3" t="n">
         <v>30</v>
       </c>
@@ -756,11 +704,7 @@
           <t>Romantic Lipbalm</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="5" t="n">
         <v>30</v>
       </c>
@@ -775,11 +719,7 @@
           <t>Strawberry Lipbalm</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="3" t="n">
         <v>30</v>
       </c>
@@ -794,11 +734,7 @@
           <t>Simple Lipbalm</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B17" s="4" t="inlineStr"/>
       <c r="C17" s="5" t="n">
         <v>20</v>
       </c>
@@ -813,11 +749,7 @@
           <t>Lipglosser - Magic Lipgloss</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="3" t="n">
         <v>30</v>
       </c>
@@ -832,11 +764,7 @@
           <t>Lipglosser - Adoge Cithas Lipgloss</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B19" s="4" t="inlineStr"/>
       <c r="C19" s="5" t="n">
         <v>80</v>
       </c>
@@ -851,11 +779,7 @@
           <t>Lipglosser - Absolute Lipgloss</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="3" t="n">
         <v>30</v>
       </c>
@@ -870,11 +794,7 @@
           <t>Lipglosser - Squeeze n Shine</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B21" s="4" t="inlineStr"/>
       <c r="C21" s="5" t="n">
         <v>30</v>
       </c>
@@ -889,11 +809,7 @@
           <t>Lipglosser - Mood Lipgloss</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="3" t="n">
         <v>30</v>
       </c>
@@ -908,11 +824,7 @@
           <t>Lipglosser - VC Small Lipgloss</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B23" s="4" t="inlineStr"/>
       <c r="C23" s="5" t="n">
         <v>15</v>
       </c>
@@ -927,11 +839,7 @@
           <t>Lip Oil - Normal</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="3" t="n">
         <v>70</v>
       </c>
@@ -946,11 +854,7 @@
           <t>Lip Oil - With a Charm</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Lip Care</t>
-        </is>
-      </c>
+      <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="5" t="n">
         <v>200</v>
       </c>
@@ -965,11 +869,7 @@
           <t>Men Wallets</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="3" t="n">
         <v>200</v>
       </c>
@@ -984,11 +884,7 @@
           <t>Ladies Wallets</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B27" s="4" t="inlineStr"/>
       <c r="C27" s="5" t="n">
         <v>100</v>
       </c>
@@ -1003,11 +899,7 @@
           <t>Anklets</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="3" t="n">
         <v>50</v>
       </c>
@@ -1022,11 +914,7 @@
           <t>Tinkles</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B29" s="4" t="inlineStr"/>
       <c r="C29" s="5" t="n">
         <v>50</v>
       </c>
@@ -1041,11 +929,7 @@
           <t>Key Holders</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="3" t="n">
         <v>200</v>
       </c>
@@ -1060,11 +944,7 @@
           <t>Phone Charms</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B31" s="4" t="inlineStr"/>
       <c r="C31" s="5" t="n">
         <v>150</v>
       </c>
@@ -1079,11 +959,7 @@
           <t>Nosering - Metallic</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="3" t="n">
         <v>10</v>
       </c>
@@ -1098,11 +974,7 @@
           <t>Nosering - Plastic</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B33" s="4" t="inlineStr"/>
       <c r="C33" s="5" t="n">
         <v>10</v>
       </c>
@@ -1117,11 +989,7 @@
           <t>Plastic Earrings</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="3" t="n">
         <v>10</v>
       </c>
@@ -1136,11 +1004,7 @@
           <t>Body Piercing Stainless</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B35" s="4" t="inlineStr"/>
       <c r="C35" s="5" t="n">
         <v>30</v>
       </c>
@@ -1155,11 +1019,7 @@
           <t>Pocket Mirror</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="3" t="n">
         <v>20</v>
       </c>
@@ -1174,11 +1034,7 @@
           <t>Pocket Mirror (Small)</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B37" s="4" t="inlineStr"/>
       <c r="C37" s="5" t="n">
         <v>50</v>
       </c>
@@ -1193,11 +1049,7 @@
           <t>Pocket Mirror (Big)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="3" t="n">
         <v>5</v>
       </c>
@@ -1212,11 +1064,7 @@
           <t>Gift Boxes / Watches</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B39" s="4" t="inlineStr"/>
       <c r="C39" s="5" t="n">
         <v>100</v>
       </c>
@@ -1231,11 +1079,7 @@
           <t>Gift Boxes</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="3" t="n">
         <v>150</v>
       </c>
@@ -1250,11 +1094,7 @@
           <t>Gift Bags (Small)</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B41" s="4" t="inlineStr"/>
       <c r="C41" s="5" t="n">
         <v>30</v>
       </c>
@@ -1269,11 +1109,7 @@
           <t>Gift Bags (Medium)</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="3" t="n">
         <v>100</v>
       </c>
@@ -1288,11 +1124,7 @@
           <t>Gift Bags (Big)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B43" s="4" t="inlineStr"/>
       <c r="C43" s="5" t="n">
         <v>150</v>
       </c>
@@ -1307,11 +1139,7 @@
           <t>Sunglasses - Kids</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="3" t="n">
         <v>30</v>
       </c>
@@ -1326,11 +1154,7 @@
           <t>Sunglasses - Frames</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B45" s="4" t="inlineStr"/>
       <c r="C45" s="5" t="n">
         <v>110</v>
       </c>
@@ -1345,11 +1169,7 @@
           <t>Sunglasses - Mens</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="3" t="n">
         <v>110</v>
       </c>
@@ -1364,11 +1184,7 @@
           <t>Sunglasses - Ladies</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B47" s="4" t="inlineStr"/>
       <c r="C47" s="5" t="n">
         <v>100</v>
       </c>
@@ -1383,11 +1199,7 @@
           <t>Sunglasses - Old Skool</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
+      <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="3" t="n">
         <v>120</v>
       </c>
@@ -1402,11 +1214,7 @@
           <t>Hairbonnet with Strings</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B49" s="4" t="inlineStr"/>
       <c r="C49" s="5" t="n">
         <v>70</v>
       </c>
@@ -1421,11 +1229,7 @@
           <t>Hair Bonnet without Strings</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="3" t="n">
         <v>50</v>
       </c>
@@ -1440,11 +1244,7 @@
           <t>Wig Caps</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B51" s="4" t="inlineStr"/>
       <c r="C51" s="5" t="n">
         <v>20</v>
       </c>
@@ -1459,11 +1259,7 @@
           <t>Headbands - Material Big</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="3" t="n">
         <v>70</v>
       </c>
@@ -1478,11 +1274,7 @@
           <t>Headbands - Material Small</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B53" s="4" t="inlineStr"/>
       <c r="C53" s="5" t="n">
         <v>35</v>
       </c>
@@ -1497,11 +1289,7 @@
           <t>Pushback - Metallic</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="3" t="n">
         <v>70</v>
       </c>
@@ -1516,11 +1304,7 @@
           <t>Pushback - Crystals</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B55" s="4" t="inlineStr"/>
       <c r="C55" s="5" t="n">
         <v>100</v>
       </c>
@@ -1535,11 +1319,7 @@
           <t>Pushback - Pins</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="3" t="n">
         <v>60</v>
       </c>
@@ -1554,11 +1334,7 @@
           <t>Kids Pushbacks</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B57" s="4" t="inlineStr"/>
       <c r="C57" s="5" t="n">
         <v>25</v>
       </c>
@@ -1573,11 +1349,7 @@
           <t>Fascinators</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="3" t="n">
         <v>350</v>
       </c>
@@ -1592,11 +1364,7 @@
           <t>Hair Ribbons</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B59" s="4" t="inlineStr"/>
       <c r="C59" s="5" t="n">
         <v>100</v>
       </c>
@@ -1611,11 +1379,7 @@
           <t>Material (Branche)</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="3" t="n">
         <v>100</v>
       </c>
@@ -1630,11 +1394,7 @@
           <t>Haircharms</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B61" s="4" t="inlineStr"/>
       <c r="C61" s="5" t="n">
         <v>10</v>
       </c>
@@ -1649,11 +1409,7 @@
           <t>Moana Clips (Small)</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="3" t="n">
         <v>15</v>
       </c>
@@ -1668,11 +1424,7 @@
           <t>Oval Clips</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B63" s="4" t="inlineStr"/>
       <c r="C63" s="5" t="n">
         <v>15</v>
       </c>
@@ -1687,11 +1439,7 @@
           <t>Fancy Metallic Clips</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="3" t="n">
         <v>15</v>
       </c>
@@ -1706,11 +1454,7 @@
           <t>Mouth Clips</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B65" s="4" t="inlineStr"/>
       <c r="C65" s="5" t="n">
         <v>30</v>
       </c>
@@ -1725,11 +1469,7 @@
           <t>Arrow Clip</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="3" t="n">
         <v>30</v>
       </c>
@@ -1744,11 +1484,7 @@
           <t>Donut Band</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B67" s="4" t="inlineStr"/>
       <c r="C67" s="5" t="n">
         <v>50</v>
       </c>
@@ -1763,11 +1499,7 @@
           <t>Bronches (Small)</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="3" t="n">
         <v>100</v>
       </c>
@@ -1782,11 +1514,7 @@
           <t>Bronches (Medium)</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B69" s="4" t="inlineStr"/>
       <c r="C69" s="5" t="n">
         <v>30</v>
       </c>
@@ -1801,11 +1529,7 @@
           <t>Hairband (Small)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="3" t="n">
         <v>50</v>
       </c>
@@ -1820,11 +1544,7 @@
           <t>Hairband - Medium (Korea)</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B71" s="4" t="inlineStr"/>
       <c r="C71" s="5" t="n">
         <v>15</v>
       </c>
@@ -1839,11 +1559,7 @@
           <t>Hairband (Big)</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="3" t="n">
         <v>15</v>
       </c>
@@ -1858,11 +1574,7 @@
           <t>Bobby Pin / Hair Pins</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B73" s="4" t="inlineStr"/>
       <c r="C73" s="5" t="n">
         <v>5</v>
       </c>
@@ -1877,11 +1589,7 @@
           <t>Bobby Pin (Big)</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Hair Accessories</t>
-        </is>
-      </c>
+      <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="3" t="n">
         <v>30</v>
       </c>
@@ -1896,11 +1604,7 @@
           <t>Hair Brush (Small)</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B75" s="4" t="inlineStr"/>
       <c r="C75" s="5" t="n">
         <v>150</v>
       </c>
@@ -1915,11 +1619,7 @@
           <t>Hair Brush (Big)</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="3" t="n">
         <v>200</v>
       </c>
@@ -1934,11 +1634,7 @@
           <t>Grey Hair Dye Pen</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B77" s="4" t="inlineStr"/>
       <c r="C77" s="5" t="n">
         <v>160</v>
       </c>
@@ -1953,11 +1649,7 @@
           <t>Hairgel - Movit</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="3" t="n">
         <v>350</v>
       </c>
@@ -1972,11 +1664,7 @@
           <t>Hairgel - Sofree Free Gel</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B79" s="4" t="inlineStr"/>
       <c r="C79" s="5" t="n">
         <v>170</v>
       </c>
@@ -1991,11 +1679,7 @@
           <t>Hairgel - Nice n Lovely</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="3" t="n">
         <v>160</v>
       </c>
@@ -2010,11 +1694,7 @@
           <t>Dexe Hair Shampoo</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B81" s="4" t="inlineStr"/>
       <c r="C81" s="5" t="n">
         <v>30</v>
       </c>
@@ -2029,11 +1709,7 @@
           <t>Bonding Glue (Small)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="3" t="n">
         <v>100</v>
       </c>
@@ -2048,11 +1724,7 @@
           <t>Bonding Glue (Big)</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B83" s="4" t="inlineStr"/>
       <c r="C83" s="5" t="n">
         <v>120</v>
       </c>
@@ -2067,11 +1739,7 @@
           <t>Hair Cutters (Small)</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="3" t="n">
         <v>20</v>
       </c>
@@ -2086,11 +1754,7 @@
           <t>Hair Cutters (Big)</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B85" s="4" t="inlineStr"/>
       <c r="C85" s="5" t="n">
         <v>30</v>
       </c>
@@ -2105,11 +1769,7 @@
           <t>Hair Comb - Tail Comb</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="3" t="n">
         <v>10</v>
       </c>
@@ -2124,11 +1784,7 @@
           <t>Hair Comb - 3 in 1</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B87" s="4" t="inlineStr"/>
       <c r="C87" s="5" t="n">
         <v>20</v>
       </c>
@@ -2143,11 +1799,7 @@
           <t>Hair Comb - Alex Comb</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="3" t="n">
         <v>25</v>
       </c>
@@ -2162,11 +1814,7 @@
           <t>Hair Comb - 2 in 1</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B89" s="4" t="inlineStr"/>
       <c r="C89" s="5" t="n">
         <v>30</v>
       </c>
@@ -2181,11 +1829,7 @@
           <t>Subane</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Hair Care</t>
-        </is>
-      </c>
+      <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="3" t="n">
         <v>50</v>
       </c>
@@ -2200,11 +1844,7 @@
           <t>Bathing Gloves</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B91" s="4" t="inlineStr"/>
       <c r="C91" s="5" t="n">
         <v>80</v>
       </c>
@@ -2219,11 +1859,7 @@
           <t>Body Scrubber Rope</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="3" t="n">
         <v>50</v>
       </c>
@@ -2238,11 +1874,7 @@
           <t>Foot Scrubbers</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B93" s="4" t="inlineStr"/>
       <c r="C93" s="5" t="n">
         <v>80</v>
       </c>
@@ -2257,11 +1889,7 @@
           <t>Asante Soap</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="3" t="n">
         <v>60</v>
       </c>
@@ -2276,11 +1904,7 @@
           <t>Pumice Stones</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B95" s="4" t="inlineStr"/>
       <c r="C95" s="5" t="n">
         <v>100</v>
       </c>
@@ -2295,11 +1919,7 @@
           <t>Signature Body Splash (Small 59ml)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="3" t="n">
         <v>100</v>
       </c>
@@ -2314,11 +1934,7 @@
           <t>Signature Body Splash (Big 236ml)</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B97" s="4" t="inlineStr"/>
       <c r="C97" s="5" t="n">
         <v>200</v>
       </c>
@@ -2333,11 +1949,7 @@
           <t>Dear Ladys</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="3" t="n">
         <v>300</v>
       </c>
@@ -2352,11 +1964,7 @@
           <t>Body Mists</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Body Care</t>
-        </is>
-      </c>
+      <c r="B99" s="4" t="inlineStr"/>
       <c r="C99" s="5" t="n">
         <v>300</v>
       </c>
@@ -2371,11 +1979,7 @@
           <t>Tumeric Oils</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="3" t="n">
         <v>200</v>
       </c>
@@ -2390,11 +1994,7 @@
           <t>Egyptian Serum</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B101" s="4" t="inlineStr"/>
       <c r="C101" s="5" t="n">
         <v>250</v>
       </c>
@@ -2409,11 +2009,7 @@
           <t>Moroccan Serum</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="3" t="n">
         <v>250</v>
       </c>
@@ -2428,11 +2024,7 @@
           <t>Dr Rashel Serum</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B103" s="4" t="inlineStr"/>
       <c r="C103" s="5" t="n">
         <v>250</v>
       </c>
@@ -2447,11 +2039,7 @@
           <t>Estelin Sunscreen</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="3" t="n">
         <v>250</v>
       </c>
@@ -2466,11 +2054,7 @@
           <t>Dr Rashel Sunscreen</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B105" s="4" t="inlineStr"/>
       <c r="C105" s="5" t="n">
         <v>250</v>
       </c>
@@ -2485,11 +2069,7 @@
           <t>Vitamin C Serum</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="3" t="n">
         <v>300</v>
       </c>
@@ -2504,11 +2084,7 @@
           <t>Rose Water</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B107" s="4" t="inlineStr"/>
       <c r="C107" s="5" t="n">
         <v>150</v>
       </c>
@@ -2523,11 +2099,7 @@
           <t>Aloe Vera Gel (Small)</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="3" t="n">
         <v>120</v>
       </c>
@@ -2542,11 +2114,7 @@
           <t>Aloe Vera Gel (Medium)</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Skin Care</t>
-        </is>
-      </c>
+      <c r="B109" s="4" t="inlineStr"/>
       <c r="C109" s="5" t="n">
         <v>200</v>
       </c>
@@ -2561,11 +2129,7 @@
           <t>Kajal Eyeliner</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="3" t="n">
         <v>40</v>
       </c>
@@ -2580,11 +2144,7 @@
           <t>Make Up Set (Small)</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B111" s="4" t="inlineStr"/>
       <c r="C111" s="5" t="n">
         <v>100</v>
       </c>
@@ -2599,11 +2159,7 @@
           <t>Make Up Set (Big)</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="3" t="n">
         <v>150</v>
       </c>
@@ -2618,11 +2174,7 @@
           <t>Concealor Brush One Sided</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B113" s="4" t="inlineStr"/>
       <c r="C113" s="5" t="n">
         <v>20</v>
       </c>
@@ -2637,11 +2189,7 @@
           <t>Concealor Brush Two Sided</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="3" t="n">
         <v>50</v>
       </c>
@@ -2656,11 +2204,7 @@
           <t>Duthan Mascara</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B115" s="4" t="inlineStr"/>
       <c r="C115" s="5" t="n">
         <v>30</v>
       </c>
@@ -2675,11 +2219,7 @@
           <t>2 in 1 Mascara</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="3" t="n">
         <v>25</v>
       </c>
@@ -2694,11 +2234,7 @@
           <t>Make Up Sponge (Round)</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B117" s="4" t="inlineStr"/>
       <c r="C117" s="5" t="n">
         <v>20</v>
       </c>
@@ -2713,11 +2249,7 @@
           <t>Make Up Sponge 2 in 1</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="3" t="n">
         <v>15</v>
       </c>
@@ -2732,11 +2264,7 @@
           <t>Lady Blue</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B119" s="4" t="inlineStr"/>
       <c r="C119" s="5" t="n">
         <v>50</v>
       </c>
@@ -2751,11 +2279,7 @@
           <t>Lock Sponge</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B120" s="2" t="inlineStr"/>
       <c r="C120" s="3" t="n">
         <v>120</v>
       </c>
@@ -2770,11 +2294,7 @@
           <t>Eyeshadow (5 in 1)</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B121" s="4" t="inlineStr"/>
       <c r="C121" s="5" t="n">
         <v>250</v>
       </c>
@@ -2789,11 +2309,7 @@
           <t>Eyeshadow Pallet</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B122" s="2" t="inlineStr"/>
       <c r="C122" s="3" t="n">
         <v>400</v>
       </c>
@@ -2808,11 +2324,7 @@
           <t>Beauty Blender</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B123" s="4" t="inlineStr"/>
       <c r="C123" s="5" t="n">
         <v>40</v>
       </c>
@@ -2827,11 +2339,7 @@
           <t>Twizers</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B124" s="2" t="inlineStr"/>
       <c r="C124" s="3" t="n">
         <v>50</v>
       </c>
@@ -2846,11 +2354,7 @@
           <t>Concealer Brush Small</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B125" s="4" t="inlineStr"/>
       <c r="C125" s="5" t="n">
         <v>30</v>
       </c>
@@ -2865,11 +2369,7 @@
           <t>Etaloner Pencil</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B126" s="2" t="inlineStr"/>
       <c r="C126" s="3" t="n">
         <v>30</v>
       </c>
@@ -2884,11 +2384,7 @@
           <t>Cappenci - Normal</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B127" s="4" t="inlineStr"/>
       <c r="C127" s="5" t="n">
         <v>20</v>
       </c>
@@ -2903,11 +2399,7 @@
           <t>Cappenci - Bold/Liner</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B128" s="2" t="inlineStr"/>
       <c r="C128" s="3" t="n">
         <v>35</v>
       </c>
@@ -2922,11 +2414,7 @@
           <t>Compact Powder - Sleek Pod (Single)</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B129" s="4" t="inlineStr"/>
       <c r="C129" s="5" t="n">
         <v>10</v>
       </c>
@@ -2941,11 +2429,7 @@
           <t>Compact Powder - Milani Pods</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B130" s="2" t="inlineStr"/>
       <c r="C130" s="3" t="n">
         <v>200</v>
       </c>
@@ -2960,11 +2444,7 @@
           <t>Compact Powder - A Face</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B131" s="4" t="inlineStr"/>
       <c r="C131" s="5" t="n">
         <v>150</v>
       </c>
@@ -2979,11 +2459,7 @@
           <t>Compact Powder - Green Tea</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B132" s="2" t="inlineStr"/>
       <c r="C132" s="3" t="n">
         <v>50</v>
       </c>
@@ -2998,11 +2474,7 @@
           <t>Compact Powder - Sleek 2 in 1</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B133" s="4" t="inlineStr"/>
       <c r="C133" s="5" t="n">
         <v>130</v>
       </c>
@@ -3017,11 +2489,7 @@
           <t>Compact Powder - Roseleaf (Small)</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B134" s="2" t="inlineStr"/>
       <c r="C134" s="3" t="n">
         <v>130</v>
       </c>
@@ -3036,11 +2504,7 @@
           <t>Compact Powder - Roseleaf (Medium)</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B135" s="4" t="inlineStr"/>
       <c r="C135" s="5" t="n">
         <v>50</v>
       </c>
@@ -3055,11 +2519,7 @@
           <t>Compact Powder - Roseleaf (Big)</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Cosmetics</t>
-        </is>
-      </c>
+      <c r="B136" s="2" t="inlineStr"/>
       <c r="C136" s="3" t="n">
         <v>70</v>
       </c>
@@ -3074,11 +2534,7 @@
           <t>Nail Files (Big)</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B137" s="4" t="inlineStr"/>
       <c r="C137" s="5" t="n">
         <v>50</v>
       </c>
@@ -3093,11 +2549,7 @@
           <t>Nail Files (Small)</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B138" s="2" t="inlineStr"/>
       <c r="C138" s="3" t="n">
         <v>30</v>
       </c>
@@ -3112,11 +2564,7 @@
           <t>Nail Brusher</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B139" s="4" t="inlineStr"/>
       <c r="C139" s="5" t="n">
         <v>30</v>
       </c>
@@ -3131,11 +2579,7 @@
           <t>Nail Glue - Brush On</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B140" s="2" t="inlineStr"/>
       <c r="C140" s="3" t="n">
         <v>60</v>
       </c>
@@ -3150,11 +2594,7 @@
           <t>Nail Glue - Yoo</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B141" s="4" t="inlineStr"/>
       <c r="C141" s="5" t="n">
         <v>160</v>
       </c>
@@ -3169,11 +2609,7 @@
           <t>Nail Glue - Small</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B142" s="2" t="inlineStr"/>
       <c r="C142" s="3" t="n">
         <v>15</v>
       </c>
@@ -3188,11 +2624,7 @@
           <t>Qutex (Small)</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B143" s="4" t="inlineStr"/>
       <c r="C143" s="5" t="n">
         <v>15</v>
       </c>
@@ -3207,11 +2639,7 @@
           <t>Qutex (Big)</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B144" s="2" t="inlineStr"/>
       <c r="C144" s="3" t="n">
         <v>30</v>
       </c>
@@ -3226,11 +2654,7 @@
           <t>Sticker Nails</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B145" s="4" t="inlineStr"/>
       <c r="C145" s="5" t="n">
         <v>30</v>
       </c>
@@ -3245,11 +2669,7 @@
           <t>Tips</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Nail Care</t>
-        </is>
-      </c>
+      <c r="B146" s="2" t="inlineStr"/>
       <c r="C146" s="3" t="n">
         <v>20</v>
       </c>
@@ -3264,11 +2684,7 @@
           <t>Caflon Earring Original</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B147" s="4" t="inlineStr"/>
       <c r="C147" s="5" t="n">
         <v>70</v>
       </c>
@@ -3283,11 +2699,7 @@
           <t>Caflon Earring Fake</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B148" s="2" t="inlineStr"/>
       <c r="C148" s="3" t="n">
         <v>20</v>
       </c>
@@ -3302,11 +2714,7 @@
           <t>Magnetic Earrings</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B149" s="4" t="inlineStr"/>
       <c r="C149" s="5" t="n">
         <v>35</v>
       </c>
@@ -3321,11 +2729,7 @@
           <t>Earrings - Loops</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B150" s="2" t="inlineStr"/>
       <c r="C150" s="3" t="n">
         <v>15</v>
       </c>
@@ -3340,11 +2744,7 @@
           <t>Earrings - Stud</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B151" s="4" t="inlineStr"/>
       <c r="C151" s="5" t="n">
         <v>15</v>
       </c>
@@ -3359,11 +2759,7 @@
           <t>Earrings - Hanging</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B152" s="2" t="inlineStr"/>
       <c r="C152" s="3" t="n">
         <v>30</v>
       </c>
@@ -3378,11 +2774,7 @@
           <t>Earrings - Chunky</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B153" s="4" t="inlineStr"/>
       <c r="C153" s="5" t="n">
         <v>100</v>
       </c>
@@ -3397,11 +2789,7 @@
           <t>Earrings - Coated</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B154" s="2" t="inlineStr"/>
       <c r="C154" s="3" t="n">
         <v>100</v>
       </c>
@@ -3416,11 +2804,7 @@
           <t>Earrings - Stainless</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
-        <is>
-          <t>Earrings</t>
-        </is>
-      </c>
+      <c r="B155" s="4" t="inlineStr"/>
       <c r="C155" s="5" t="n">
         <v>30</v>
       </c>
@@ -3435,11 +2819,7 @@
           <t>Chains (Giver)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B156" s="2" t="inlineStr"/>
       <c r="C156" s="3" t="n">
         <v>100</v>
       </c>
@@ -3454,11 +2834,7 @@
           <t>Gold Earrings Ladies</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B157" s="4" t="inlineStr"/>
       <c r="C157" s="5" t="n">
         <v>100</v>
       </c>
@@ -3473,11 +2849,7 @@
           <t>Bracelet (Charms Stainless)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B158" s="2" t="inlineStr"/>
       <c r="C158" s="3" t="n">
         <v>150</v>
       </c>
@@ -3492,11 +2864,7 @@
           <t>Gold Chain Mens</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B159" s="4" t="inlineStr"/>
       <c r="C159" s="5" t="n">
         <v>200</v>
       </c>
@@ -3511,11 +2879,7 @@
           <t>Fancy Chain Ladies</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B160" s="2" t="inlineStr"/>
       <c r="C160" s="3" t="n">
         <v>120</v>
       </c>
@@ -3530,11 +2894,7 @@
           <t>Earring and Chain Set</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B161" s="4" t="inlineStr"/>
       <c r="C161" s="5" t="n">
         <v>150</v>
       </c>
@@ -3549,11 +2909,7 @@
           <t>Rings - Mid Rings</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B162" s="2" t="inlineStr"/>
       <c r="C162" s="3" t="n">
         <v>30</v>
       </c>
@@ -3568,11 +2924,7 @@
           <t>Rings - Engagement Ring</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B163" s="4" t="inlineStr"/>
       <c r="C163" s="5" t="n">
         <v>35</v>
       </c>
@@ -3587,11 +2939,7 @@
           <t>Rings - Wedding Ring</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B164" s="2" t="inlineStr"/>
       <c r="C164" s="3" t="n">
         <v>50</v>
       </c>
@@ -3606,11 +2954,7 @@
           <t>Rings - Chunky Rings</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Jewellery</t>
-        </is>
-      </c>
+      <c r="B165" s="4" t="inlineStr"/>
       <c r="C165" s="5" t="n">
         <v>150</v>
       </c>
@@ -3625,11 +2969,7 @@
           <t>Smart Collections Perfumer</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>Perfumes</t>
-        </is>
-      </c>
+      <c r="B166" s="2" t="inlineStr"/>
       <c r="C166" s="3" t="n">
         <v>120</v>
       </c>
@@ -3644,11 +2984,7 @@
           <t>Crown Perfumes</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>Perfumes</t>
-        </is>
-      </c>
+      <c r="B167" s="4" t="inlineStr"/>
       <c r="C167" s="5" t="n">
         <v>100</v>
       </c>
@@ -3663,11 +2999,7 @@
           <t>Pen Spray (Ceriflone)</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>Perfumes</t>
-        </is>
-      </c>
+      <c r="B168" s="2" t="inlineStr"/>
       <c r="C168" s="3" t="n">
         <v>75</v>
       </c>
@@ -3682,11 +3014,7 @@
           <t>Invisible Bra</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B169" s="4" t="inlineStr"/>
       <c r="C169" s="5" t="n">
         <v>150</v>
       </c>
@@ -3701,11 +3029,7 @@
           <t>Bra Straps</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B170" s="2" t="inlineStr"/>
       <c r="C170" s="3" t="n">
         <v>30</v>
       </c>
@@ -3720,11 +3044,7 @@
           <t>Handkerchiefs</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B171" s="4" t="inlineStr"/>
       <c r="C171" s="5" t="n">
         <v>30</v>
       </c>
@@ -3739,11 +3059,7 @@
           <t>Belts - Slim Ladies</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B172" s="2" t="inlineStr"/>
       <c r="C172" s="3" t="n">
         <v>70</v>
       </c>
@@ -3758,11 +3074,7 @@
           <t>Belts - Bacon Ladies</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B173" s="4" t="inlineStr"/>
       <c r="C173" s="5" t="n">
         <v>110</v>
       </c>
@@ -3777,11 +3089,7 @@
           <t>Belts - Men Belts</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B174" s="2" t="inlineStr"/>
       <c r="C174" s="3" t="n">
         <v>120</v>
       </c>
@@ -3796,11 +3104,7 @@
           <t>Belts - Elastic Belts</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B175" s="4" t="inlineStr"/>
       <c r="C175" s="5" t="n">
         <v>130</v>
       </c>
@@ -3815,11 +3119,7 @@
           <t>Panties - Kids</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B176" s="2" t="inlineStr"/>
       <c r="C176" s="3" t="n">
         <v>150</v>
       </c>
@@ -3834,11 +3134,7 @@
           <t>Panties - G-Strings</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B177" s="4" t="inlineStr"/>
       <c r="C177" s="5" t="n">
         <v>160</v>
       </c>
@@ -3853,11 +3149,7 @@
           <t>Panties - Thongs</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B178" s="2" t="inlineStr"/>
       <c r="C178" s="3" t="n">
         <v>150</v>
       </c>
@@ -3872,11 +3164,7 @@
           <t>Panties - Normals</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B179" s="4" t="inlineStr"/>
       <c r="C179" s="5" t="n">
         <v>150</v>
       </c>
@@ -3891,11 +3179,7 @@
           <t>Ankle Socks</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B180" s="2" t="inlineStr"/>
       <c r="C180" s="3" t="n">
         <v>30</v>
       </c>
@@ -3910,11 +3194,7 @@
           <t>Ankle Socks Cottons</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B181" s="4" t="inlineStr"/>
       <c r="C181" s="5" t="n">
         <v>35</v>
       </c>
@@ -3929,11 +3209,7 @@
           <t>Fishnet Stockings</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B182" s="2" t="inlineStr"/>
       <c r="C182" s="3" t="n">
         <v>120</v>
       </c>
@@ -3948,11 +3224,7 @@
           <t>Normal Stockings (Mtumike)</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+      <c r="B183" s="4" t="inlineStr"/>
       <c r="C183" s="5" t="n">
         <v>50</v>
       </c>
@@ -3967,11 +3239,7 @@
           <t>Watches (Wrist)</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>Watches</t>
-        </is>
-      </c>
+      <c r="B184" s="2" t="inlineStr"/>
       <c r="C184" s="3" t="n">
         <v>10</v>
       </c>
@@ -3986,11 +3254,7 @@
           <t>Magnetic Watches</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>Watches</t>
-        </is>
-      </c>
+      <c r="B185" s="4" t="inlineStr"/>
       <c r="C185" s="5" t="n">
         <v>165</v>
       </c>
@@ -4005,11 +3269,7 @@
           <t>Rubber Watches</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>Watches</t>
-        </is>
-      </c>
+      <c r="B186" s="2" t="inlineStr"/>
       <c r="C186" s="3" t="n">
         <v>130</v>
       </c>
@@ -4024,11 +3284,7 @@
           <t>Metallic Watches</t>
         </is>
       </c>
-      <c r="B187" s="4" t="inlineStr">
-        <is>
-          <t>Watches</t>
-        </is>
-      </c>
+      <c r="B187" s="4" t="inlineStr"/>
       <c r="C187" s="5" t="n">
         <v>250</v>
       </c>
@@ -4043,11 +3299,7 @@
           <t>Kids Watches</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>Watches</t>
-        </is>
-      </c>
+      <c r="B188" s="2" t="inlineStr"/>
       <c r="C188" s="3" t="n">
         <v>100</v>
       </c>
@@ -4062,11 +3314,7 @@
           <t>Razorblades</t>
         </is>
       </c>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
+      <c r="B189" s="4" t="inlineStr"/>
       <c r="C189" s="5" t="n">
         <v>3</v>
       </c>
@@ -4081,11 +3329,7 @@
           <t>Durex</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
+      <c r="B190" s="2" t="inlineStr"/>
       <c r="C190" s="3" t="n">
         <v>100</v>
       </c>
@@ -4100,11 +3344,7 @@
           <t>Portable Fan (Small)</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
+      <c r="B191" s="4" t="inlineStr"/>
       <c r="C191" s="5" t="n">
         <v>250</v>
       </c>
@@ -4119,11 +3359,7 @@
           <t>Portable Fan (Big)</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
+      <c r="B192" s="2" t="inlineStr"/>
       <c r="C192" s="3" t="n">
         <v>300</v>
       </c>
@@ -4138,11 +3374,7 @@
           <t>Sling Bag - Fluffy Sling</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B193" s="4" t="inlineStr"/>
       <c r="C193" s="5" t="n">
         <v>300</v>
       </c>
@@ -4157,11 +3389,7 @@
           <t>Sling Bag with a Ribbon</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B194" s="2" t="inlineStr"/>
       <c r="C194" s="3" t="n">
         <v>400</v>
       </c>
@@ -4176,11 +3404,7 @@
           <t>Min Min Small Sling Bag</t>
         </is>
       </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B195" s="4" t="inlineStr"/>
       <c r="C195" s="5" t="n">
         <v>550</v>
       </c>
@@ -4195,11 +3419,7 @@
           <t>2 in 1 Sling Bag (Leather)</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B196" s="2" t="inlineStr"/>
       <c r="C196" s="3" t="n">
         <v>1000</v>
       </c>
@@ -4214,11 +3434,7 @@
           <t>Sling Bag (Plain)</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B197" s="4" t="inlineStr"/>
       <c r="C197" s="5" t="n">
         <v>700</v>
       </c>
@@ -4233,11 +3449,7 @@
           <t>Unisex Sling Bag</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B198" s="2" t="inlineStr"/>
       <c r="C198" s="3" t="n">
         <v>250</v>
       </c>
@@ -4252,11 +3464,7 @@
           <t>Waist Bag (Small)</t>
         </is>
       </c>
-      <c r="B199" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B199" s="4" t="inlineStr"/>
       <c r="C199" s="5" t="n">
         <v>100</v>
       </c>
@@ -4271,11 +3479,7 @@
           <t>Waist Bag (Big)</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B200" s="2" t="inlineStr"/>
       <c r="C200" s="3" t="n">
         <v>300</v>
       </c>
@@ -4290,11 +3494,7 @@
           <t>Student Tote Bags</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B201" s="4" t="inlineStr"/>
       <c r="C201" s="5" t="n">
         <v>500</v>
       </c>
@@ -4309,11 +3509,7 @@
           <t>Travelling Bags</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B202" s="2" t="inlineStr"/>
       <c r="C202" s="3" t="n">
         <v>500</v>
       </c>
@@ -4328,11 +3524,7 @@
           <t>Dolla Bag</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B203" s="4" t="inlineStr"/>
       <c r="C203" s="5" t="n">
         <v>500</v>
       </c>
@@ -4347,11 +3539,7 @@
           <t>2 in 1 Bag Tote Bag</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B204" s="2" t="inlineStr"/>
       <c r="C204" s="3" t="n">
         <v>400</v>
       </c>
@@ -4366,11 +3554,7 @@
           <t>Tote Bag with a Matching Hat</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B205" s="4" t="inlineStr"/>
       <c r="C205" s="5" t="n">
         <v>400</v>
       </c>
@@ -4385,11 +3569,7 @@
           <t>Queen Bags</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B206" s="2" t="inlineStr"/>
       <c r="C206" s="3" t="n">
         <v>350</v>
       </c>
@@ -4404,11 +3584,7 @@
           <t>Straw Bag / Same Bag with a Hat</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B207" s="4" t="inlineStr"/>
       <c r="C207" s="5" t="n">
         <v>1100</v>
       </c>
@@ -4423,11 +3599,7 @@
           <t>Jute Bag / Woven Bag</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B208" s="2" t="inlineStr"/>
       <c r="C208" s="3" t="n">
         <v>300</v>
       </c>
@@ -4442,11 +3614,7 @@
           <t>Partitioned Tote Bags</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B209" s="4" t="inlineStr"/>
       <c r="C209" s="5" t="n">
         <v>600</v>
       </c>
@@ -4461,11 +3629,7 @@
           <t>Plain Partitioned Bag (Medium)</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B210" s="2" t="inlineStr"/>
       <c r="C210" s="3" t="n">
         <v>650</v>
       </c>
@@ -4480,11 +3644,7 @@
           <t>Summer Bags (Vibes)</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B211" s="4" t="inlineStr"/>
       <c r="C211" s="5" t="n">
         <v>500</v>
       </c>
@@ -4499,11 +3659,7 @@
           <t>Mothers Bag</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B212" s="2" t="inlineStr"/>
       <c r="C212" s="3" t="n">
         <v>1100</v>
       </c>
@@ -4518,11 +3674,7 @@
           <t>GA Tote Bag</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B213" s="4" t="inlineStr"/>
       <c r="C213" s="5" t="n">
         <v>1100</v>
       </c>
@@ -4537,11 +3689,7 @@
           <t>Fendi Tote Bag</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B214" s="2" t="inlineStr"/>
       <c r="C214" s="3" t="n">
         <v>1000</v>
       </c>
@@ -4556,11 +3704,7 @@
           <t>Official Bag 2 in 1</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B215" s="4" t="inlineStr"/>
       <c r="C215" s="5" t="n">
         <v>1200</v>
       </c>
@@ -4575,11 +3719,7 @@
           <t>Minmin Bag Medium (Original)</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B216" s="2" t="inlineStr"/>
       <c r="C216" s="3" t="n">
         <v>1200</v>
       </c>
@@ -4594,11 +3734,7 @@
           <t>Coach Leather Bag</t>
         </is>
       </c>
-      <c r="B217" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B217" s="4" t="inlineStr"/>
       <c r="C217" s="5" t="n">
         <v>1100</v>
       </c>
@@ -4613,11 +3749,7 @@
           <t>Burberry Bag</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B218" s="2" t="inlineStr"/>
       <c r="C218" s="3" t="n">
         <v>750</v>
       </c>
@@ -4632,11 +3764,7 @@
           <t>Chain Tote Bag</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B219" s="4" t="inlineStr"/>
       <c r="C219" s="5" t="n">
         <v>750</v>
       </c>
@@ -4651,11 +3779,7 @@
           <t>3 in 1 Official Bag</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B220" s="2" t="inlineStr"/>
       <c r="C220" s="3" t="n">
         <v>1000</v>
       </c>
@@ -4670,11 +3794,7 @@
           <t>5 in 1 Bags</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B221" s="4" t="inlineStr"/>
       <c r="C221" s="5" t="n">
         <v>1800</v>
       </c>
@@ -4689,11 +3809,7 @@
           <t>4 in 1 Bags</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B222" s="2" t="inlineStr"/>
       <c r="C222" s="3" t="n">
         <v>1700</v>
       </c>
@@ -4708,11 +3824,7 @@
           <t>Monkey Bag Flowered</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B223" s="4" t="inlineStr"/>
       <c r="C223" s="5" t="n">
         <v>650</v>
       </c>
@@ -4727,11 +3839,7 @@
           <t>Monkey Bag Plain</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B224" s="2" t="inlineStr"/>
       <c r="C224" s="3" t="n">
         <v>1000</v>
       </c>
@@ -4746,11 +3854,7 @@
           <t>Minmin Big Bag</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B225" s="4" t="inlineStr"/>
       <c r="C225" s="5" t="n">
         <v>700</v>
       </c>
@@ -4765,11 +3869,7 @@
           <t>Cellophone Bag</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B226" s="2" t="inlineStr"/>
       <c r="C226" s="3" t="n">
         <v>300</v>
       </c>
@@ -4784,11 +3884,7 @@
           <t>Cello Phone Bag (Small)</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
+      <c r="B227" s="4" t="inlineStr"/>
       <c r="C227" s="5" t="n">
         <v>250</v>
       </c>

--- a/products_import.xlsx
+++ b/products_import.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Products" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$E$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$O$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
@@ -72,16 +72,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D1D5DB"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
@@ -466,40 +466,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:O227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Buying Price</t>
+          <t>supplier</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Selling Price</t>
+          <t>buyingPrice</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>sellingPrice</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>wholesalePrice</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dealerPrice</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lowStockThreshold</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>reorderLevel</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>measure</t>
         </is>
       </c>
     </row>
@@ -509,14 +569,24 @@
           <t>Eyelashes - Cluster Lasher</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -524,14 +594,24 @@
           <t>Eyelashes - Striper Lashes</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr"/>
-      <c r="C3" s="5" t="n">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="E3" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -539,14 +619,24 @@
           <t>Eyelashes - Striper Small Lashes</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -554,14 +644,24 @@
           <t>Foundation - Green Tea</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
-      <c r="C5" s="5" t="n">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -569,14 +669,24 @@
           <t>Foundation - Sleek</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="3" t="n">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -584,14 +694,24 @@
           <t>Foundation - Blackopal</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="5" t="n">
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -599,14 +719,24 @@
           <t>Primers</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="3" t="n">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -614,14 +744,24 @@
           <t>Concealors</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="5" t="n">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="E9" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -629,14 +769,24 @@
           <t>Liquid Matte Lipsticks</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="3" t="n">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -644,14 +794,24 @@
           <t>Irene Lipstick</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="5" t="n">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="E11" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -659,14 +819,24 @@
           <t>Normal Matte Lipstick</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="3" t="n">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -674,14 +844,24 @@
           <t>Vaseline Lipbalm</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="5" t="n">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
+      <c r="E13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -689,14 +869,24 @@
           <t>Roll-on Lipbalm</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -704,14 +894,24 @@
           <t>Romantic Lipbalm</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="5" t="n">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -719,14 +919,24 @@
           <t>Strawberry Lipbalm</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -734,14 +944,24 @@
           <t>Simple Lipbalm</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="5" t="n">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="E17" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -749,14 +969,24 @@
           <t>Lipglosser - Magic Lipgloss</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -764,14 +994,24 @@
           <t>Lipglosser - Adoge Cithas Lipgloss</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="5" t="n">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="E19" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -779,14 +1019,24 @@
           <t>Lipglosser - Absolute Lipgloss</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -794,14 +1044,24 @@
           <t>Lipglosser - Squeeze n Shine</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-      <c r="C21" s="5" t="n">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -809,14 +1069,24 @@
           <t>Lipglosser - Mood Lipgloss</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr"/>
-      <c r="C22" s="3" t="n">
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -824,14 +1094,24 @@
           <t>Lipglosser - VC Small Lipgloss</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="5" t="n">
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="E23" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -839,14 +1119,24 @@
           <t>Lip Oil - Normal</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr"/>
-      <c r="C24" s="3" t="n">
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -854,14 +1144,24 @@
           <t>Lip Oil - With a Charm</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr"/>
-      <c r="C25" s="5" t="n">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="E25" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -869,14 +1169,24 @@
           <t>Men Wallets</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="3" t="n">
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -884,14 +1194,24 @@
           <t>Ladies Wallets</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
       <c r="D27" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -899,14 +1219,24 @@
           <t>Anklets</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr"/>
-      <c r="C28" s="3" t="n">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -914,14 +1244,24 @@
           <t>Tinkles</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="5" t="n">
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="E29" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -929,14 +1269,24 @@
           <t>Key Holders</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="3" t="n">
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -944,14 +1294,24 @@
           <t>Phone Charms</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="5" t="n">
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="E31" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -959,14 +1319,24 @@
           <t>Nosering - Metallic</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="3" t="n">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -974,14 +1344,24 @@
           <t>Nosering - Plastic</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr"/>
-      <c r="C33" s="5" t="n">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="E33" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -989,14 +1369,24 @@
           <t>Plastic Earrings</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr"/>
-      <c r="C34" s="3" t="n">
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1004,14 +1394,24 @@
           <t>Body Piercing Stainless</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr"/>
-      <c r="C35" s="5" t="n">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1019,14 +1419,24 @@
           <t>Pocket Mirror</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="3" t="n">
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -1034,14 +1444,24 @@
           <t>Pocket Mirror (Small)</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr"/>
-      <c r="C37" s="5" t="n">
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="E37" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1049,14 +1469,24 @@
           <t>Pocket Mirror (Big)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="3" t="n">
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -1064,14 +1494,24 @@
           <t>Gift Boxes / Watches</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
       <c r="D39" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E39" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1079,14 +1519,24 @@
           <t>Gift Boxes</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="3" t="n">
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="n"/>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -1094,14 +1544,24 @@
           <t>Gift Bags (Small)</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr"/>
-      <c r="C41" s="5" t="n">
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D41" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="E41" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1109,14 +1569,24 @@
           <t>Gift Bags (Medium)</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E42" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1124,14 +1594,24 @@
           <t>Gift Bags (Big)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr"/>
-      <c r="C43" s="5" t="n">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="E43" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n"/>
+      <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1139,14 +1619,24 @@
           <t>Sunglasses - Kids</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr"/>
-      <c r="C44" s="3" t="n">
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -1154,14 +1644,24 @@
           <t>Sunglasses - Frames</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="5" t="n">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="E45" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1169,14 +1669,24 @@
           <t>Sunglasses - Mens</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="3" t="n">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1184,14 +1694,24 @@
           <t>Sunglasses - Ladies</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr"/>
-      <c r="C47" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1199,14 +1719,24 @@
           <t>Sunglasses - Old Skool</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="3" t="n">
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -1214,14 +1744,24 @@
           <t>Hairbonnet with Strings</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr"/>
-      <c r="C49" s="5" t="n">
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="E49" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1229,14 +1769,24 @@
           <t>Hair Bonnet without Strings</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr"/>
-      <c r="C50" s="3" t="n">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -1244,14 +1794,24 @@
           <t>Wig Caps</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr"/>
-      <c r="C51" s="5" t="n">
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D51" s="5" t="n">
+      <c r="E51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1259,14 +1819,24 @@
           <t>Headbands - Material Big</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr"/>
-      <c r="C52" s="3" t="n">
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -1274,14 +1844,24 @@
           <t>Headbands - Material Small</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr"/>
-      <c r="C53" s="5" t="n">
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D53" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E53" s="4" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1289,14 +1869,24 @@
           <t>Pushback - Metallic</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" s="3" t="n">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -1304,14 +1894,24 @@
           <t>Pushback - Crystals</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr"/>
-      <c r="C55" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
       <c r="D55" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1319,14 +1919,24 @@
           <t>Pushback - Pins</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="3" t="n">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -1334,14 +1944,24 @@
           <t>Kids Pushbacks</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr"/>
-      <c r="C57" s="5" t="n">
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="D57" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1349,14 +1969,24 @@
           <t>Fascinators</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" s="3" t="n">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -1364,14 +1994,24 @@
           <t>Hair Ribbons</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr"/>
-      <c r="C59" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
       <c r="D59" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E59" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="n"/>
+      <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1379,14 +2019,24 @@
           <t>Material (Branche)</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr"/>
-      <c r="C60" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
       <c r="D60" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -1394,14 +2044,24 @@
           <t>Haircharms</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr"/>
-      <c r="C61" s="5" t="n">
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="4" t="n"/>
+      <c r="D61" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D61" s="5" t="n">
+      <c r="E61" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="E61" s="4" t="inlineStr"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1409,14 +2069,24 @@
           <t>Moana Clips (Small)</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="3" t="n">
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="E62" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n"/>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -1424,14 +2094,24 @@
           <t>Oval Clips</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr"/>
-      <c r="C63" s="5" t="n">
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D63" s="5" t="n">
+      <c r="E63" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E63" s="4" t="inlineStr"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1439,14 +2119,24 @@
           <t>Fancy Metallic Clips</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="3" t="n">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="E64" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -1454,14 +2144,24 @@
           <t>Mouth Clips</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr"/>
-      <c r="C65" s="5" t="n">
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D65" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E65" s="4" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1469,14 +2169,24 @@
           <t>Arrow Clip</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="3" t="n">
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+      <c r="E66" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -1484,14 +2194,24 @@
           <t>Donut Band</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr"/>
-      <c r="C67" s="5" t="n">
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D67" s="5" t="n">
+      <c r="E67" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1499,14 +2219,24 @@
           <t>Bronches (Small)</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
       <c r="D68" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E68" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n"/>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -1514,14 +2244,24 @@
           <t>Bronches (Medium)</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr"/>
-      <c r="C69" s="5" t="n">
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D69" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E69" s="4" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+      <c r="M69" s="4" t="n"/>
+      <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1529,14 +2269,24 @@
           <t>Hairband (Small)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr"/>
-      <c r="C70" s="3" t="n">
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="E70" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+      <c r="J70" s="2" t="n"/>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="2" t="n"/>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -1544,14 +2294,24 @@
           <t>Hairband - Medium (Korea)</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr"/>
-      <c r="C71" s="5" t="n">
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D71" s="5" t="n">
+      <c r="E71" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -1559,14 +2319,24 @@
           <t>Hairband (Big)</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="3" t="n">
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="E72" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -1574,14 +2344,24 @@
           <t>Bobby Pin / Hair Pins</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="5" t="n">
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D73" s="5" t="n">
+      <c r="E73" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="J73" s="4" t="n"/>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -1589,14 +2369,24 @@
           <t>Bobby Pin (Big)</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr"/>
-      <c r="C74" s="3" t="n">
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D74" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
+      <c r="I74" s="2" t="n"/>
+      <c r="J74" s="2" t="n"/>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="2" t="n"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -1604,14 +2394,24 @@
           <t>Hair Brush (Small)</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr"/>
-      <c r="C75" s="5" t="n">
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="E75" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+      <c r="L75" s="4" t="n"/>
+      <c r="M75" s="4" t="n"/>
+      <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -1619,14 +2419,24 @@
           <t>Hair Brush (Big)</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="3" t="n">
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="E76" s="3" t="n">
         <v>450</v>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n"/>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -1634,14 +2444,24 @@
           <t>Grey Hair Dye Pen</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr"/>
-      <c r="C77" s="5" t="n">
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="E77" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n"/>
+      <c r="L77" s="4" t="n"/>
+      <c r="M77" s="4" t="n"/>
+      <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -1649,14 +2469,24 @@
           <t>Hairgel - Movit</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="3" t="n">
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="E78" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -1664,14 +2494,24 @@
           <t>Hairgel - Sofree Free Gel</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr"/>
-      <c r="C79" s="5" t="n">
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="E79" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E79" s="4" t="inlineStr"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="n"/>
+      <c r="L79" s="4" t="n"/>
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -1679,14 +2519,24 @@
           <t>Hairgel - Nice n Lovely</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="3" t="n">
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="E80" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -1694,14 +2544,24 @@
           <t>Dexe Hair Shampoo</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr"/>
-      <c r="C81" s="5" t="n">
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D81" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E81" s="4" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="4" t="n"/>
+      <c r="K81" s="4" t="n"/>
+      <c r="L81" s="4" t="n"/>
+      <c r="M81" s="4" t="n"/>
+      <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -1709,14 +2569,24 @@
           <t>Bonding Glue (Small)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr"/>
-      <c r="C82" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
       <c r="D82" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E82" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -1724,14 +2594,24 @@
           <t>Bonding Glue (Big)</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr"/>
-      <c r="C83" s="5" t="n">
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="D83" s="5" t="n">
+      <c r="E83" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="n"/>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="n"/>
+      <c r="L83" s="4" t="n"/>
+      <c r="M83" s="4" t="n"/>
+      <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -1739,14 +2619,24 @@
           <t>Hair Cutters (Small)</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr"/>
-      <c r="C84" s="3" t="n">
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="E84" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -1754,14 +2644,24 @@
           <t>Hair Cutters (Big)</t>
         </is>
       </c>
-      <c r="B85" s="4" t="inlineStr"/>
-      <c r="C85" s="5" t="n">
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D85" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E85" s="4" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="J85" s="4" t="n"/>
+      <c r="K85" s="4" t="n"/>
+      <c r="L85" s="4" t="n"/>
+      <c r="M85" s="4" t="n"/>
+      <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -1769,14 +2669,24 @@
           <t>Hair Comb - Tail Comb</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr"/>
-      <c r="C86" s="3" t="n">
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="E86" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n"/>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -1784,14 +2694,24 @@
           <t>Hair Comb - 3 in 1</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr"/>
-      <c r="C87" s="5" t="n">
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D87" s="5" t="n">
+      <c r="E87" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E87" s="4" t="inlineStr"/>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
+      <c r="K87" s="4" t="n"/>
+      <c r="L87" s="4" t="n"/>
+      <c r="M87" s="4" t="n"/>
+      <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -1799,14 +2719,24 @@
           <t>Hair Comb - Alex Comb</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr"/>
-      <c r="C88" s="3" t="n">
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D88" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E88" s="2" t="inlineStr"/>
+      <c r="E88" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -1814,14 +2744,24 @@
           <t>Hair Comb - 2 in 1</t>
         </is>
       </c>
-      <c r="B89" s="4" t="inlineStr"/>
-      <c r="C89" s="5" t="n">
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D89" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E89" s="4" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -1829,14 +2769,24 @@
           <t>Subane</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr"/>
-      <c r="C90" s="3" t="n">
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D90" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="E90" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+      <c r="J90" s="2" t="n"/>
+      <c r="K90" s="2" t="n"/>
+      <c r="L90" s="2" t="n"/>
+      <c r="M90" s="2" t="n"/>
+      <c r="N90" s="2" t="n"/>
+      <c r="O90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -1844,14 +2794,24 @@
           <t>Bathing Gloves</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr"/>
-      <c r="C91" s="5" t="n">
+      <c r="B91" s="4" t="n"/>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="D91" s="5" t="n">
+      <c r="E91" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E91" s="4" t="inlineStr"/>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="n"/>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="n"/>
+      <c r="J91" s="4" t="n"/>
+      <c r="K91" s="4" t="n"/>
+      <c r="L91" s="4" t="n"/>
+      <c r="M91" s="4" t="n"/>
+      <c r="N91" s="4" t="n"/>
+      <c r="O91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -1859,14 +2819,24 @@
           <t>Body Scrubber Rope</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr"/>
-      <c r="C92" s="3" t="n">
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="E92" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="2" t="n"/>
+      <c r="L92" s="2" t="n"/>
+      <c r="M92" s="2" t="n"/>
+      <c r="N92" s="2" t="n"/>
+      <c r="O92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -1874,14 +2844,24 @@
           <t>Foot Scrubbers</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr"/>
-      <c r="C93" s="5" t="n">
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="D93" s="5" t="n">
+      <c r="E93" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E93" s="4" t="inlineStr"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -1889,14 +2869,24 @@
           <t>Asante Soap</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr"/>
-      <c r="C94" s="3" t="n">
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="E94" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
+      <c r="J94" s="2" t="n"/>
+      <c r="K94" s="2" t="n"/>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="2" t="n"/>
+      <c r="N94" s="2" t="n"/>
+      <c r="O94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -1904,14 +2894,24 @@
           <t>Pumice Stones</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr"/>
-      <c r="C95" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
       <c r="D95" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E95" s="4" t="inlineStr"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -1919,14 +2919,24 @@
           <t>Signature Body Splash (Small 59ml)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr"/>
-      <c r="C96" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
       <c r="D96" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E96" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+      <c r="J96" s="2" t="n"/>
+      <c r="K96" s="2" t="n"/>
+      <c r="L96" s="2" t="n"/>
+      <c r="M96" s="2" t="n"/>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -1934,14 +2944,24 @@
           <t>Signature Body Splash (Big 236ml)</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr"/>
-      <c r="C97" s="5" t="n">
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D97" s="5" t="n">
+      <c r="E97" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E97" s="4" t="inlineStr"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="n"/>
+      <c r="H97" s="4" t="n"/>
+      <c r="I97" s="4" t="n"/>
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="n"/>
+      <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1949,14 +2969,24 @@
           <t>Dear Ladys</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr"/>
-      <c r="C98" s="3" t="n">
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="E98" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="n"/>
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -1964,14 +2994,24 @@
           <t>Body Mists</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr"/>
-      <c r="C99" s="5" t="n">
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="D99" s="5" t="n">
+      <c r="E99" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E99" s="4" t="inlineStr"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="n"/>
+      <c r="H99" s="4" t="n"/>
+      <c r="I99" s="4" t="n"/>
+      <c r="J99" s="4" t="n"/>
+      <c r="K99" s="4" t="n"/>
+      <c r="L99" s="4" t="n"/>
+      <c r="M99" s="4" t="n"/>
+      <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -1979,14 +3019,24 @@
           <t>Tumeric Oils</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr"/>
-      <c r="C100" s="3" t="n">
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="E100" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="2" t="n"/>
+      <c r="L100" s="2" t="n"/>
+      <c r="M100" s="2" t="n"/>
+      <c r="N100" s="2" t="n"/>
+      <c r="O100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -1994,14 +3044,24 @@
           <t>Egyptian Serum</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr"/>
-      <c r="C101" s="5" t="n">
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D101" s="5" t="n">
+      <c r="E101" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E101" s="4" t="inlineStr"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+      <c r="H101" s="4" t="n"/>
+      <c r="I101" s="4" t="n"/>
+      <c r="J101" s="4" t="n"/>
+      <c r="K101" s="4" t="n"/>
+      <c r="L101" s="4" t="n"/>
+      <c r="M101" s="4" t="n"/>
+      <c r="N101" s="4" t="n"/>
+      <c r="O101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2009,14 +3069,24 @@
           <t>Moroccan Serum</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr"/>
-      <c r="C102" s="3" t="n">
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="E102" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
+      <c r="J102" s="2" t="n"/>
+      <c r="K102" s="2" t="n"/>
+      <c r="L102" s="2" t="n"/>
+      <c r="M102" s="2" t="n"/>
+      <c r="N102" s="2" t="n"/>
+      <c r="O102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -2024,14 +3094,24 @@
           <t>Dr Rashel Serum</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr"/>
-      <c r="C103" s="5" t="n">
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D103" s="5" t="n">
+      <c r="E103" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="n"/>
+      <c r="H103" s="4" t="n"/>
+      <c r="I103" s="4" t="n"/>
+      <c r="J103" s="4" t="n"/>
+      <c r="K103" s="4" t="n"/>
+      <c r="L103" s="4" t="n"/>
+      <c r="M103" s="4" t="n"/>
+      <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2039,14 +3119,24 @@
           <t>Estelin Sunscreen</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr"/>
-      <c r="C104" s="3" t="n">
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="E104" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="2" t="n"/>
+      <c r="L104" s="2" t="n"/>
+      <c r="M104" s="2" t="n"/>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -2054,14 +3144,24 @@
           <t>Dr Rashel Sunscreen</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr"/>
-      <c r="C105" s="5" t="n">
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D105" s="5" t="n">
+      <c r="E105" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E105" s="4" t="inlineStr"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="4" t="n"/>
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="n"/>
+      <c r="L105" s="4" t="n"/>
+      <c r="M105" s="4" t="n"/>
+      <c r="N105" s="4" t="n"/>
+      <c r="O105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2069,14 +3169,24 @@
           <t>Vitamin C Serum</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr"/>
-      <c r="C106" s="3" t="n">
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="E106" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="n"/>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -2084,14 +3194,24 @@
           <t>Rose Water</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr"/>
-      <c r="C107" s="5" t="n">
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D107" s="5" t="n">
+      <c r="E107" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E107" s="4" t="inlineStr"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="n"/>
+      <c r="L107" s="4" t="n"/>
+      <c r="M107" s="4" t="n"/>
+      <c r="N107" s="4" t="n"/>
+      <c r="O107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2099,14 +3219,24 @@
           <t>Aloe Vera Gel (Small)</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr"/>
-      <c r="C108" s="3" t="n">
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="E108" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="2" t="n"/>
+      <c r="H108" s="2" t="n"/>
+      <c r="I108" s="2" t="n"/>
+      <c r="J108" s="2" t="n"/>
+      <c r="K108" s="2" t="n"/>
+      <c r="L108" s="2" t="n"/>
+      <c r="M108" s="2" t="n"/>
+      <c r="N108" s="2" t="n"/>
+      <c r="O108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -2114,14 +3244,24 @@
           <t>Aloe Vera Gel (Medium)</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr"/>
-      <c r="C109" s="5" t="n">
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D109" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="n"/>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="4" t="n"/>
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="n"/>
+      <c r="L109" s="4" t="n"/>
+      <c r="M109" s="4" t="n"/>
+      <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2129,14 +3269,24 @@
           <t>Kajal Eyeliner</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr"/>
-      <c r="C110" s="3" t="n">
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="D110" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="E110" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="n"/>
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -2144,14 +3294,24 @@
           <t>Make Up Set (Small)</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr"/>
-      <c r="C111" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
       <c r="D111" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E111" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E111" s="4" t="inlineStr"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="n"/>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="4" t="n"/>
+      <c r="J111" s="4" t="n"/>
+      <c r="K111" s="4" t="n"/>
+      <c r="L111" s="4" t="n"/>
+      <c r="M111" s="4" t="n"/>
+      <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2159,14 +3319,24 @@
           <t>Make Up Set (Big)</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr"/>
-      <c r="C112" s="3" t="n">
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="E112" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -2174,14 +3344,24 @@
           <t>Concealor Brush One Sided</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr"/>
-      <c r="C113" s="5" t="n">
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D113" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E113" s="4" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="n"/>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="4" t="n"/>
+      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="n"/>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
+      <c r="N113" s="4" t="n"/>
+      <c r="O113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2189,14 +3369,24 @@
           <t>Concealor Brush Two Sided</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr"/>
-      <c r="C114" s="3" t="n">
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="E114" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -2204,14 +3394,24 @@
           <t>Duthan Mascara</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr"/>
-      <c r="C115" s="5" t="n">
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D115" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E115" s="4" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2219,14 +3419,24 @@
           <t>2 in 1 Mascara</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr"/>
-      <c r="C116" s="3" t="n">
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="D116" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
+      <c r="E116" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
+      <c r="J116" s="2" t="n"/>
+      <c r="K116" s="2" t="n"/>
+      <c r="L116" s="2" t="n"/>
+      <c r="M116" s="2" t="n"/>
+      <c r="N116" s="2" t="n"/>
+      <c r="O116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -2234,14 +3444,24 @@
           <t>Make Up Sponge (Round)</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr"/>
-      <c r="C117" s="5" t="n">
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D117" s="5" t="n">
+      <c r="E117" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E117" s="4" t="inlineStr"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="4" t="n"/>
+      <c r="J117" s="4" t="n"/>
+      <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="n"/>
+      <c r="M117" s="4" t="n"/>
+      <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2249,14 +3469,24 @@
           <t>Make Up Sponge 2 in 1</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr"/>
-      <c r="C118" s="3" t="n">
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="E118" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="2" t="n"/>
+      <c r="L118" s="2" t="n"/>
+      <c r="M118" s="2" t="n"/>
+      <c r="N118" s="2" t="n"/>
+      <c r="O118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -2264,14 +3494,24 @@
           <t>Lady Blue</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr"/>
-      <c r="C119" s="5" t="n">
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D119" s="5" t="n">
+      <c r="E119" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E119" s="4" t="inlineStr"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
+      <c r="K119" s="4" t="n"/>
+      <c r="L119" s="4" t="n"/>
+      <c r="M119" s="4" t="n"/>
+      <c r="N119" s="4" t="n"/>
+      <c r="O119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2279,14 +3519,24 @@
           <t>Lock Sponge</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr"/>
-      <c r="C120" s="3" t="n">
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="E120" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="2" t="n"/>
+      <c r="L120" s="2" t="n"/>
+      <c r="M120" s="2" t="n"/>
+      <c r="N120" s="2" t="n"/>
+      <c r="O120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -2294,14 +3544,24 @@
           <t>Eyeshadow (5 in 1)</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr"/>
-      <c r="C121" s="5" t="n">
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D121" s="5" t="n">
+      <c r="E121" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E121" s="4" t="inlineStr"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
+      <c r="O121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -2309,14 +3569,24 @@
           <t>Eyeshadow Pallet</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr"/>
-      <c r="C122" s="3" t="n">
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="E122" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
+      <c r="J122" s="2" t="n"/>
+      <c r="K122" s="2" t="n"/>
+      <c r="L122" s="2" t="n"/>
+      <c r="M122" s="2" t="n"/>
+      <c r="N122" s="2" t="n"/>
+      <c r="O122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -2324,14 +3594,24 @@
           <t>Beauty Blender</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr"/>
-      <c r="C123" s="5" t="n">
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D123" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E123" s="4" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="n"/>
+      <c r="J123" s="4" t="n"/>
+      <c r="K123" s="4" t="n"/>
+      <c r="L123" s="4" t="n"/>
+      <c r="M123" s="4" t="n"/>
+      <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -2339,14 +3619,24 @@
           <t>Twizers</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr"/>
-      <c r="C124" s="3" t="n">
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D124" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E124" s="2" t="inlineStr"/>
+      <c r="E124" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="n"/>
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -2354,14 +3644,24 @@
           <t>Concealer Brush Small</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr"/>
-      <c r="C125" s="5" t="n">
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D125" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E125" s="4" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="4" t="n"/>
+      <c r="J125" s="4" t="n"/>
+      <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
+      <c r="N125" s="4" t="n"/>
+      <c r="O125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -2369,14 +3669,24 @@
           <t>Etaloner Pencil</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr"/>
-      <c r="C126" s="3" t="n">
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D126" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E126" s="2" t="inlineStr"/>
+      <c r="E126" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
+      <c r="K126" s="2" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="2" t="n"/>
+      <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -2384,14 +3694,24 @@
           <t>Cappenci - Normal</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr"/>
-      <c r="C127" s="5" t="n">
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D127" s="5" t="n">
+      <c r="E127" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E127" s="4" t="inlineStr"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
+      <c r="K127" s="4" t="n"/>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
+      <c r="N127" s="4" t="n"/>
+      <c r="O127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -2399,14 +3719,24 @@
           <t>Cappenci - Bold/Liner</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr"/>
-      <c r="C128" s="3" t="n">
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="D128" s="3" t="n">
+      <c r="E128" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
+      <c r="J128" s="2" t="n"/>
+      <c r="K128" s="2" t="n"/>
+      <c r="L128" s="2" t="n"/>
+      <c r="M128" s="2" t="n"/>
+      <c r="N128" s="2" t="n"/>
+      <c r="O128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -2414,14 +3744,24 @@
           <t>Compact Powder - Sleek Pod (Single)</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr"/>
-      <c r="C129" s="5" t="n">
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D129" s="5" t="n">
+      <c r="E129" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E129" s="4" t="inlineStr"/>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="n"/>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="4" t="n"/>
+      <c r="J129" s="4" t="n"/>
+      <c r="K129" s="4" t="n"/>
+      <c r="L129" s="4" t="n"/>
+      <c r="M129" s="4" t="n"/>
+      <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -2429,14 +3769,24 @@
           <t>Compact Powder - Milani Pods</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr"/>
-      <c r="C130" s="3" t="n">
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="E130" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -2444,14 +3794,24 @@
           <t>Compact Powder - A Face</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr"/>
-      <c r="C131" s="5" t="n">
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D131" s="5" t="n">
+      <c r="E131" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E131" s="4" t="inlineStr"/>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="n"/>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="4" t="n"/>
+      <c r="J131" s="4" t="n"/>
+      <c r="K131" s="4" t="n"/>
+      <c r="L131" s="4" t="n"/>
+      <c r="M131" s="4" t="n"/>
+      <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -2459,14 +3819,24 @@
           <t>Compact Powder - Green Tea</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr"/>
-      <c r="C132" s="3" t="n">
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D132" s="3" t="n">
+      <c r="E132" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="2" t="n"/>
+      <c r="L132" s="2" t="n"/>
+      <c r="M132" s="2" t="n"/>
+      <c r="N132" s="2" t="n"/>
+      <c r="O132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -2474,14 +3844,24 @@
           <t>Compact Powder - Sleek 2 in 1</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr"/>
-      <c r="C133" s="5" t="n">
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="D133" s="5" t="n">
+      <c r="E133" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E133" s="4" t="inlineStr"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="n"/>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="4" t="n"/>
+      <c r="J133" s="4" t="n"/>
+      <c r="K133" s="4" t="n"/>
+      <c r="L133" s="4" t="n"/>
+      <c r="M133" s="4" t="n"/>
+      <c r="N133" s="4" t="n"/>
+      <c r="O133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -2489,14 +3869,24 @@
           <t>Compact Powder - Roseleaf (Small)</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr"/>
-      <c r="C134" s="3" t="n">
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="D134" s="3" t="n">
+      <c r="E134" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="n"/>
+      <c r="O134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -2504,14 +3894,24 @@
           <t>Compact Powder - Roseleaf (Medium)</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr"/>
-      <c r="C135" s="5" t="n">
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D135" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E135" s="4" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
+      <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -2519,14 +3919,24 @@
           <t>Compact Powder - Roseleaf (Big)</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr"/>
-      <c r="C136" s="3" t="n">
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="D136" s="3" t="n">
+      <c r="E136" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="n"/>
+      <c r="H136" s="2" t="n"/>
+      <c r="I136" s="2" t="n"/>
+      <c r="J136" s="2" t="n"/>
+      <c r="K136" s="2" t="n"/>
+      <c r="L136" s="2" t="n"/>
+      <c r="M136" s="2" t="n"/>
+      <c r="N136" s="2" t="n"/>
+      <c r="O136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -2534,14 +3944,24 @@
           <t>Nail Files (Big)</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr"/>
-      <c r="C137" s="5" t="n">
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D137" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E137" s="4" t="inlineStr"/>
+      <c r="E137" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="n"/>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="4" t="n"/>
+      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="n"/>
+      <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -2549,14 +3969,24 @@
           <t>Nail Files (Small)</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr"/>
-      <c r="C138" s="3" t="n">
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D138" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E138" s="2" t="inlineStr"/>
+      <c r="E138" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="n"/>
+      <c r="K138" s="2" t="n"/>
+      <c r="L138" s="2" t="n"/>
+      <c r="M138" s="2" t="n"/>
+      <c r="N138" s="2" t="n"/>
+      <c r="O138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -2564,14 +3994,24 @@
           <t>Nail Brusher</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr"/>
-      <c r="C139" s="5" t="n">
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D139" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E139" s="4" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="n"/>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="4" t="n"/>
+      <c r="J139" s="4" t="n"/>
+      <c r="K139" s="4" t="n"/>
+      <c r="L139" s="4" t="n"/>
+      <c r="M139" s="4" t="n"/>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -2579,14 +4019,24 @@
           <t>Nail Glue - Brush On</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr"/>
-      <c r="C140" s="3" t="n">
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D140" s="3" t="n">
+      <c r="E140" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
+      <c r="J140" s="2" t="n"/>
+      <c r="K140" s="2" t="n"/>
+      <c r="L140" s="2" t="n"/>
+      <c r="M140" s="2" t="n"/>
+      <c r="N140" s="2" t="n"/>
+      <c r="O140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -2594,14 +4044,24 @@
           <t>Nail Glue - Yoo</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr"/>
-      <c r="C141" s="5" t="n">
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D141" s="5" t="n">
+      <c r="E141" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E141" s="4" t="inlineStr"/>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="n"/>
+      <c r="J141" s="4" t="n"/>
+      <c r="K141" s="4" t="n"/>
+      <c r="L141" s="4" t="n"/>
+      <c r="M141" s="4" t="n"/>
+      <c r="N141" s="4" t="n"/>
+      <c r="O141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -2609,14 +4069,24 @@
           <t>Nail Glue - Small</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr"/>
-      <c r="C142" s="3" t="n">
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D142" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E142" s="2" t="inlineStr"/>
+      <c r="E142" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
+      <c r="L142" s="2" t="n"/>
+      <c r="M142" s="2" t="n"/>
+      <c r="N142" s="2" t="n"/>
+      <c r="O142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -2624,14 +4094,24 @@
           <t>Qutex (Small)</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr"/>
-      <c r="C143" s="5" t="n">
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D143" s="5" t="n">
+      <c r="E143" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E143" s="4" t="inlineStr"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
+      <c r="L143" s="4" t="n"/>
+      <c r="M143" s="4" t="n"/>
+      <c r="N143" s="4" t="n"/>
+      <c r="O143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -2639,14 +4119,24 @@
           <t>Qutex (Big)</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr"/>
-      <c r="C144" s="3" t="n">
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D144" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E144" s="2" t="inlineStr"/>
+      <c r="E144" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F144" s="2" t="n"/>
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="2" t="n"/>
+      <c r="N144" s="2" t="n"/>
+      <c r="O144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -2654,14 +4144,24 @@
           <t>Sticker Nails</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr"/>
-      <c r="C145" s="5" t="n">
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D145" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E145" s="4" t="inlineStr"/>
+      <c r="E145" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="J145" s="4" t="n"/>
+      <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -2669,14 +4169,24 @@
           <t>Tips</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr"/>
-      <c r="C146" s="3" t="n">
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="E146" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="2" t="n"/>
+      <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+      <c r="J146" s="2" t="n"/>
+      <c r="K146" s="2" t="n"/>
+      <c r="L146" s="2" t="n"/>
+      <c r="M146" s="2" t="n"/>
+      <c r="N146" s="2" t="n"/>
+      <c r="O146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -2684,14 +4194,24 @@
           <t>Caflon Earring Original</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr"/>
-      <c r="C147" s="5" t="n">
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="D147" s="5" t="n">
+      <c r="E147" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E147" s="4" t="inlineStr"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="4" t="n"/>
+      <c r="J147" s="4" t="n"/>
+      <c r="K147" s="4" t="n"/>
+      <c r="L147" s="4" t="n"/>
+      <c r="M147" s="4" t="n"/>
+      <c r="N147" s="4" t="n"/>
+      <c r="O147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -2699,14 +4219,24 @@
           <t>Caflon Earring Fake</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr"/>
-      <c r="C148" s="3" t="n">
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="D148" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E148" s="2" t="inlineStr"/>
+      <c r="E148" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
+      <c r="K148" s="2" t="n"/>
+      <c r="L148" s="2" t="n"/>
+      <c r="M148" s="2" t="n"/>
+      <c r="N148" s="2" t="n"/>
+      <c r="O148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -2714,14 +4244,24 @@
           <t>Magnetic Earrings</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr"/>
-      <c r="C149" s="5" t="n">
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D149" s="5" t="n">
+      <c r="E149" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E149" s="4" t="inlineStr"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="n"/>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="4" t="n"/>
+      <c r="J149" s="4" t="n"/>
+      <c r="K149" s="4" t="n"/>
+      <c r="L149" s="4" t="n"/>
+      <c r="M149" s="4" t="n"/>
+      <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -2729,14 +4269,24 @@
           <t>Earrings - Loops</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr"/>
-      <c r="C150" s="3" t="n">
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="D150" s="3" t="n">
+      <c r="E150" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
+      <c r="K150" s="2" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="2" t="n"/>
+      <c r="N150" s="2" t="n"/>
+      <c r="O150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -2744,14 +4294,24 @@
           <t>Earrings - Stud</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr"/>
-      <c r="C151" s="5" t="n">
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D151" s="5" t="n">
+      <c r="E151" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E151" s="4" t="inlineStr"/>
+      <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="n"/>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="4" t="n"/>
+      <c r="J151" s="4" t="n"/>
+      <c r="K151" s="4" t="n"/>
+      <c r="L151" s="4" t="n"/>
+      <c r="M151" s="4" t="n"/>
+      <c r="N151" s="4" t="n"/>
+      <c r="O151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -2759,14 +4319,24 @@
           <t>Earrings - Hanging</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr"/>
-      <c r="C152" s="3" t="n">
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D152" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E152" s="2" t="inlineStr"/>
+      <c r="E152" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2" t="n"/>
+      <c r="J152" s="2" t="n"/>
+      <c r="K152" s="2" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="2" t="n"/>
+      <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -2774,14 +4344,24 @@
           <t>Earrings - Chunky</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr"/>
-      <c r="C153" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B153" s="4" t="n"/>
+      <c r="C153" s="4" t="n"/>
       <c r="D153" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E153" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E153" s="4" t="inlineStr"/>
+      <c r="F153" s="4" t="n"/>
+      <c r="G153" s="4" t="n"/>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="4" t="n"/>
+      <c r="J153" s="4" t="n"/>
+      <c r="K153" s="4" t="n"/>
+      <c r="L153" s="4" t="n"/>
+      <c r="M153" s="4" t="n"/>
+      <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -2789,14 +4369,24 @@
           <t>Earrings - Coated</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr"/>
-      <c r="C154" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
       <c r="D154" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E154" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="n"/>
+      <c r="G154" s="2" t="n"/>
+      <c r="H154" s="2" t="n"/>
+      <c r="I154" s="2" t="n"/>
+      <c r="J154" s="2" t="n"/>
+      <c r="K154" s="2" t="n"/>
+      <c r="L154" s="2" t="n"/>
+      <c r="M154" s="2" t="n"/>
+      <c r="N154" s="2" t="n"/>
+      <c r="O154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -2804,14 +4394,24 @@
           <t>Earrings - Stainless</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr"/>
-      <c r="C155" s="5" t="n">
+      <c r="B155" s="4" t="n"/>
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D155" s="5" t="n">
+      <c r="E155" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E155" s="4" t="inlineStr"/>
+      <c r="F155" s="4" t="n"/>
+      <c r="G155" s="4" t="n"/>
+      <c r="H155" s="4" t="n"/>
+      <c r="I155" s="4" t="n"/>
+      <c r="J155" s="4" t="n"/>
+      <c r="K155" s="4" t="n"/>
+      <c r="L155" s="4" t="n"/>
+      <c r="M155" s="4" t="n"/>
+      <c r="N155" s="4" t="n"/>
+      <c r="O155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -2819,14 +4419,24 @@
           <t>Chains (Giver)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr"/>
-      <c r="C156" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
       <c r="D156" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E156" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="n"/>
+      <c r="K156" s="2" t="n"/>
+      <c r="L156" s="2" t="n"/>
+      <c r="M156" s="2" t="n"/>
+      <c r="N156" s="2" t="n"/>
+      <c r="O156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -2834,14 +4444,24 @@
           <t>Gold Earrings Ladies</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr"/>
-      <c r="C157" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="4" t="n"/>
       <c r="D157" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E157" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E157" s="4" t="inlineStr"/>
+      <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="n"/>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="4" t="n"/>
+      <c r="J157" s="4" t="n"/>
+      <c r="K157" s="4" t="n"/>
+      <c r="L157" s="4" t="n"/>
+      <c r="M157" s="4" t="n"/>
+      <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -2849,14 +4469,24 @@
           <t>Bracelet (Charms Stainless)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr"/>
-      <c r="C158" s="3" t="n">
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="D158" s="3" t="n">
+      <c r="E158" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
+      <c r="J158" s="2" t="n"/>
+      <c r="K158" s="2" t="n"/>
+      <c r="L158" s="2" t="n"/>
+      <c r="M158" s="2" t="n"/>
+      <c r="N158" s="2" t="n"/>
+      <c r="O158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -2864,14 +4494,24 @@
           <t>Gold Chain Mens</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr"/>
-      <c r="C159" s="5" t="n">
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D159" s="5" t="n">
+      <c r="E159" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="n"/>
+      <c r="G159" s="4" t="n"/>
+      <c r="H159" s="4" t="n"/>
+      <c r="I159" s="4" t="n"/>
+      <c r="J159" s="4" t="n"/>
+      <c r="K159" s="4" t="n"/>
+      <c r="L159" s="4" t="n"/>
+      <c r="M159" s="4" t="n"/>
+      <c r="N159" s="4" t="n"/>
+      <c r="O159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -2879,14 +4519,24 @@
           <t>Fancy Chain Ladies</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr"/>
-      <c r="C160" s="3" t="n">
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D160" s="3" t="n">
+      <c r="E160" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="n"/>
+      <c r="G160" s="2" t="n"/>
+      <c r="H160" s="2" t="n"/>
+      <c r="I160" s="2" t="n"/>
+      <c r="J160" s="2" t="n"/>
+      <c r="K160" s="2" t="n"/>
+      <c r="L160" s="2" t="n"/>
+      <c r="M160" s="2" t="n"/>
+      <c r="N160" s="2" t="n"/>
+      <c r="O160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -2894,14 +4544,24 @@
           <t>Earring and Chain Set</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr"/>
-      <c r="C161" s="5" t="n">
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D161" s="5" t="n">
+      <c r="E161" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E161" s="4" t="inlineStr"/>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="4" t="n"/>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="4" t="n"/>
+      <c r="J161" s="4" t="n"/>
+      <c r="K161" s="4" t="n"/>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="4" t="n"/>
+      <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -2909,14 +4569,24 @@
           <t>Rings - Mid Rings</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr"/>
-      <c r="C162" s="3" t="n">
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D162" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E162" s="2" t="inlineStr"/>
+      <c r="E162" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F162" s="2" t="n"/>
+      <c r="G162" s="2" t="n"/>
+      <c r="H162" s="2" t="n"/>
+      <c r="I162" s="2" t="n"/>
+      <c r="J162" s="2" t="n"/>
+      <c r="K162" s="2" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="2" t="n"/>
+      <c r="N162" s="2" t="n"/>
+      <c r="O162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -2924,14 +4594,24 @@
           <t>Rings - Engagement Ring</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr"/>
-      <c r="C163" s="5" t="n">
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D163" s="5" t="n">
+      <c r="E163" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="E163" s="4" t="inlineStr"/>
+      <c r="F163" s="4" t="n"/>
+      <c r="G163" s="4" t="n"/>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="4" t="n"/>
+      <c r="J163" s="4" t="n"/>
+      <c r="K163" s="4" t="n"/>
+      <c r="L163" s="4" t="n"/>
+      <c r="M163" s="4" t="n"/>
+      <c r="N163" s="4" t="n"/>
+      <c r="O163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -2939,14 +4619,24 @@
           <t>Rings - Wedding Ring</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr"/>
-      <c r="C164" s="3" t="n">
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="E164" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="2" t="n"/>
+      <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2" t="n"/>
+      <c r="J164" s="2" t="n"/>
+      <c r="K164" s="2" t="n"/>
+      <c r="L164" s="2" t="n"/>
+      <c r="M164" s="2" t="n"/>
+      <c r="N164" s="2" t="n"/>
+      <c r="O164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -2954,14 +4644,24 @@
           <t>Rings - Chunky Rings</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr"/>
-      <c r="C165" s="5" t="n">
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D165" s="5" t="n">
+      <c r="E165" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E165" s="4" t="inlineStr"/>
+      <c r="F165" s="4" t="n"/>
+      <c r="G165" s="4" t="n"/>
+      <c r="H165" s="4" t="n"/>
+      <c r="I165" s="4" t="n"/>
+      <c r="J165" s="4" t="n"/>
+      <c r="K165" s="4" t="n"/>
+      <c r="L165" s="4" t="n"/>
+      <c r="M165" s="4" t="n"/>
+      <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -2969,14 +4669,24 @@
           <t>Smart Collections Perfumer</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr"/>
-      <c r="C166" s="3" t="n">
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D166" s="3" t="n">
+      <c r="E166" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="n"/>
+      <c r="H166" s="2" t="n"/>
+      <c r="I166" s="2" t="n"/>
+      <c r="J166" s="2" t="n"/>
+      <c r="K166" s="2" t="n"/>
+      <c r="L166" s="2" t="n"/>
+      <c r="M166" s="2" t="n"/>
+      <c r="N166" s="2" t="n"/>
+      <c r="O166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -2984,14 +4694,24 @@
           <t>Crown Perfumes</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr"/>
-      <c r="C167" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="4" t="n"/>
       <c r="D167" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E167" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E167" s="4" t="inlineStr"/>
+      <c r="F167" s="4" t="n"/>
+      <c r="G167" s="4" t="n"/>
+      <c r="H167" s="4" t="n"/>
+      <c r="I167" s="4" t="n"/>
+      <c r="J167" s="4" t="n"/>
+      <c r="K167" s="4" t="n"/>
+      <c r="L167" s="4" t="n"/>
+      <c r="M167" s="4" t="n"/>
+      <c r="N167" s="4" t="n"/>
+      <c r="O167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -2999,14 +4719,24 @@
           <t>Pen Spray (Ceriflone)</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr"/>
-      <c r="C168" s="3" t="n">
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="D168" s="3" t="n">
+      <c r="E168" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="n"/>
+      <c r="L168" s="2" t="n"/>
+      <c r="M168" s="2" t="n"/>
+      <c r="N168" s="2" t="n"/>
+      <c r="O168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -3014,14 +4744,24 @@
           <t>Invisible Bra</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr"/>
-      <c r="C169" s="5" t="n">
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D169" s="5" t="n">
+      <c r="E169" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E169" s="4" t="inlineStr"/>
+      <c r="F169" s="4" t="n"/>
+      <c r="G169" s="4" t="n"/>
+      <c r="H169" s="4" t="n"/>
+      <c r="I169" s="4" t="n"/>
+      <c r="J169" s="4" t="n"/>
+      <c r="K169" s="4" t="n"/>
+      <c r="L169" s="4" t="n"/>
+      <c r="M169" s="4" t="n"/>
+      <c r="N169" s="4" t="n"/>
+      <c r="O169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -3029,14 +4769,24 @@
           <t>Bra Straps</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr"/>
-      <c r="C170" s="3" t="n">
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D170" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E170" s="2" t="inlineStr"/>
+      <c r="E170" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="2" t="n"/>
+      <c r="H170" s="2" t="n"/>
+      <c r="I170" s="2" t="n"/>
+      <c r="J170" s="2" t="n"/>
+      <c r="K170" s="2" t="n"/>
+      <c r="L170" s="2" t="n"/>
+      <c r="M170" s="2" t="n"/>
+      <c r="N170" s="2" t="n"/>
+      <c r="O170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -3044,14 +4794,24 @@
           <t>Handkerchiefs</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr"/>
-      <c r="C171" s="5" t="n">
+      <c r="B171" s="4" t="n"/>
+      <c r="C171" s="4" t="n"/>
+      <c r="D171" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D171" s="5" t="n">
+      <c r="E171" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E171" s="4" t="inlineStr"/>
+      <c r="F171" s="4" t="n"/>
+      <c r="G171" s="4" t="n"/>
+      <c r="H171" s="4" t="n"/>
+      <c r="I171" s="4" t="n"/>
+      <c r="J171" s="4" t="n"/>
+      <c r="K171" s="4" t="n"/>
+      <c r="L171" s="4" t="n"/>
+      <c r="M171" s="4" t="n"/>
+      <c r="N171" s="4" t="n"/>
+      <c r="O171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -3059,14 +4819,24 @@
           <t>Belts - Slim Ladies</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr"/>
-      <c r="C172" s="3" t="n">
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="D172" s="3" t="n">
+      <c r="E172" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="n"/>
+      <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
+      <c r="J172" s="2" t="n"/>
+      <c r="K172" s="2" t="n"/>
+      <c r="L172" s="2" t="n"/>
+      <c r="M172" s="2" t="n"/>
+      <c r="N172" s="2" t="n"/>
+      <c r="O172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -3074,14 +4844,24 @@
           <t>Belts - Bacon Ladies</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr"/>
-      <c r="C173" s="5" t="n">
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="D173" s="5" t="n">
+      <c r="E173" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E173" s="4" t="inlineStr"/>
+      <c r="F173" s="4" t="n"/>
+      <c r="G173" s="4" t="n"/>
+      <c r="H173" s="4" t="n"/>
+      <c r="I173" s="4" t="n"/>
+      <c r="J173" s="4" t="n"/>
+      <c r="K173" s="4" t="n"/>
+      <c r="L173" s="4" t="n"/>
+      <c r="M173" s="4" t="n"/>
+      <c r="N173" s="4" t="n"/>
+      <c r="O173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -3089,14 +4869,24 @@
           <t>Belts - Men Belts</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr"/>
-      <c r="C174" s="3" t="n">
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D174" s="3" t="n">
+      <c r="E174" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="n"/>
+      <c r="G174" s="2" t="n"/>
+      <c r="H174" s="2" t="n"/>
+      <c r="I174" s="2" t="n"/>
+      <c r="J174" s="2" t="n"/>
+      <c r="K174" s="2" t="n"/>
+      <c r="L174" s="2" t="n"/>
+      <c r="M174" s="2" t="n"/>
+      <c r="N174" s="2" t="n"/>
+      <c r="O174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -3104,14 +4894,24 @@
           <t>Belts - Elastic Belts</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr"/>
-      <c r="C175" s="5" t="n">
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="D175" s="5" t="n">
+      <c r="E175" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E175" s="4" t="inlineStr"/>
+      <c r="F175" s="4" t="n"/>
+      <c r="G175" s="4" t="n"/>
+      <c r="H175" s="4" t="n"/>
+      <c r="I175" s="4" t="n"/>
+      <c r="J175" s="4" t="n"/>
+      <c r="K175" s="4" t="n"/>
+      <c r="L175" s="4" t="n"/>
+      <c r="M175" s="4" t="n"/>
+      <c r="N175" s="4" t="n"/>
+      <c r="O175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -3119,14 +4919,24 @@
           <t>Panties - Kids</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr"/>
-      <c r="C176" s="3" t="n">
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="D176" s="3" t="n">
+      <c r="E176" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="2" t="n"/>
+      <c r="H176" s="2" t="n"/>
+      <c r="I176" s="2" t="n"/>
+      <c r="J176" s="2" t="n"/>
+      <c r="K176" s="2" t="n"/>
+      <c r="L176" s="2" t="n"/>
+      <c r="M176" s="2" t="n"/>
+      <c r="N176" s="2" t="n"/>
+      <c r="O176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -3134,14 +4944,24 @@
           <t>Panties - G-Strings</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr"/>
-      <c r="C177" s="5" t="n">
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="4" t="n"/>
+      <c r="D177" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="D177" s="5" t="n">
+      <c r="E177" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="E177" s="4" t="inlineStr"/>
+      <c r="F177" s="4" t="n"/>
+      <c r="G177" s="4" t="n"/>
+      <c r="H177" s="4" t="n"/>
+      <c r="I177" s="4" t="n"/>
+      <c r="J177" s="4" t="n"/>
+      <c r="K177" s="4" t="n"/>
+      <c r="L177" s="4" t="n"/>
+      <c r="M177" s="4" t="n"/>
+      <c r="N177" s="4" t="n"/>
+      <c r="O177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -3149,14 +4969,24 @@
           <t>Panties - Thongs</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr"/>
-      <c r="C178" s="3" t="n">
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="D178" s="3" t="n">
+      <c r="E178" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="n"/>
+      <c r="H178" s="2" t="n"/>
+      <c r="I178" s="2" t="n"/>
+      <c r="J178" s="2" t="n"/>
+      <c r="K178" s="2" t="n"/>
+      <c r="L178" s="2" t="n"/>
+      <c r="M178" s="2" t="n"/>
+      <c r="N178" s="2" t="n"/>
+      <c r="O178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -3164,14 +4994,24 @@
           <t>Panties - Normals</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr"/>
-      <c r="C179" s="5" t="n">
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="D179" s="5" t="n">
+      <c r="E179" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="E179" s="4" t="inlineStr"/>
+      <c r="F179" s="4" t="n"/>
+      <c r="G179" s="4" t="n"/>
+      <c r="H179" s="4" t="n"/>
+      <c r="I179" s="4" t="n"/>
+      <c r="J179" s="4" t="n"/>
+      <c r="K179" s="4" t="n"/>
+      <c r="L179" s="4" t="n"/>
+      <c r="M179" s="4" t="n"/>
+      <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -3179,14 +5019,24 @@
           <t>Ankle Socks</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr"/>
-      <c r="C180" s="3" t="n">
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="D180" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E180" s="2" t="inlineStr"/>
+      <c r="E180" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+      <c r="J180" s="2" t="n"/>
+      <c r="K180" s="2" t="n"/>
+      <c r="L180" s="2" t="n"/>
+      <c r="M180" s="2" t="n"/>
+      <c r="N180" s="2" t="n"/>
+      <c r="O180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -3194,14 +5044,24 @@
           <t>Ankle Socks Cottons</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr"/>
-      <c r="C181" s="5" t="n">
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="D181" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E181" s="4" t="inlineStr"/>
+      <c r="E181" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F181" s="4" t="n"/>
+      <c r="G181" s="4" t="n"/>
+      <c r="H181" s="4" t="n"/>
+      <c r="I181" s="4" t="n"/>
+      <c r="J181" s="4" t="n"/>
+      <c r="K181" s="4" t="n"/>
+      <c r="L181" s="4" t="n"/>
+      <c r="M181" s="4" t="n"/>
+      <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -3209,14 +5069,24 @@
           <t>Fishnet Stockings</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr"/>
-      <c r="C182" s="3" t="n">
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="E182" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+      <c r="J182" s="2" t="n"/>
+      <c r="K182" s="2" t="n"/>
+      <c r="L182" s="2" t="n"/>
+      <c r="M182" s="2" t="n"/>
+      <c r="N182" s="2" t="n"/>
+      <c r="O182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -3224,14 +5094,24 @@
           <t>Normal Stockings (Mtumike)</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr"/>
-      <c r="C183" s="5" t="n">
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D183" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="E183" s="4" t="inlineStr"/>
+      <c r="E183" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F183" s="4" t="n"/>
+      <c r="G183" s="4" t="n"/>
+      <c r="H183" s="4" t="n"/>
+      <c r="I183" s="4" t="n"/>
+      <c r="J183" s="4" t="n"/>
+      <c r="K183" s="4" t="n"/>
+      <c r="L183" s="4" t="n"/>
+      <c r="M183" s="4" t="n"/>
+      <c r="N183" s="4" t="n"/>
+      <c r="O183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -3239,14 +5119,24 @@
           <t>Watches (Wrist)</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr"/>
-      <c r="C184" s="3" t="n">
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D184" s="3" t="n">
+      <c r="E184" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="n"/>
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="n"/>
+      <c r="I184" s="2" t="n"/>
+      <c r="J184" s="2" t="n"/>
+      <c r="K184" s="2" t="n"/>
+      <c r="L184" s="2" t="n"/>
+      <c r="M184" s="2" t="n"/>
+      <c r="N184" s="2" t="n"/>
+      <c r="O184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -3254,14 +5144,24 @@
           <t>Magnetic Watches</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr"/>
-      <c r="C185" s="5" t="n">
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="5" t="n">
         <v>165</v>
       </c>
-      <c r="D185" s="5" t="n">
+      <c r="E185" s="5" t="n">
         <v>350</v>
       </c>
-      <c r="E185" s="4" t="inlineStr"/>
+      <c r="F185" s="4" t="n"/>
+      <c r="G185" s="4" t="n"/>
+      <c r="H185" s="4" t="n"/>
+      <c r="I185" s="4" t="n"/>
+      <c r="J185" s="4" t="n"/>
+      <c r="K185" s="4" t="n"/>
+      <c r="L185" s="4" t="n"/>
+      <c r="M185" s="4" t="n"/>
+      <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -3269,14 +5169,24 @@
           <t>Rubber Watches</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr"/>
-      <c r="C186" s="3" t="n">
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="D186" s="3" t="n">
+      <c r="E186" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="n"/>
+      <c r="G186" s="2" t="n"/>
+      <c r="H186" s="2" t="n"/>
+      <c r="I186" s="2" t="n"/>
+      <c r="J186" s="2" t="n"/>
+      <c r="K186" s="2" t="n"/>
+      <c r="L186" s="2" t="n"/>
+      <c r="M186" s="2" t="n"/>
+      <c r="N186" s="2" t="n"/>
+      <c r="O186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -3284,14 +5194,24 @@
           <t>Metallic Watches</t>
         </is>
       </c>
-      <c r="B187" s="4" t="inlineStr"/>
-      <c r="C187" s="5" t="n">
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D187" s="5" t="n">
+      <c r="E187" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E187" s="4" t="inlineStr"/>
+      <c r="F187" s="4" t="n"/>
+      <c r="G187" s="4" t="n"/>
+      <c r="H187" s="4" t="n"/>
+      <c r="I187" s="4" t="n"/>
+      <c r="J187" s="4" t="n"/>
+      <c r="K187" s="4" t="n"/>
+      <c r="L187" s="4" t="n"/>
+      <c r="M187" s="4" t="n"/>
+      <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -3299,14 +5219,24 @@
           <t>Kids Watches</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr"/>
-      <c r="C188" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
       <c r="D188" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E188" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="2" t="n"/>
+      <c r="H188" s="2" t="n"/>
+      <c r="I188" s="2" t="n"/>
+      <c r="J188" s="2" t="n"/>
+      <c r="K188" s="2" t="n"/>
+      <c r="L188" s="2" t="n"/>
+      <c r="M188" s="2" t="n"/>
+      <c r="N188" s="2" t="n"/>
+      <c r="O188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -3314,14 +5244,24 @@
           <t>Razorblades</t>
         </is>
       </c>
-      <c r="B189" s="4" t="inlineStr"/>
-      <c r="C189" s="5" t="n">
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D189" s="5" t="n">
+      <c r="E189" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E189" s="4" t="inlineStr"/>
+      <c r="F189" s="4" t="n"/>
+      <c r="G189" s="4" t="n"/>
+      <c r="H189" s="4" t="n"/>
+      <c r="I189" s="4" t="n"/>
+      <c r="J189" s="4" t="n"/>
+      <c r="K189" s="4" t="n"/>
+      <c r="L189" s="4" t="n"/>
+      <c r="M189" s="4" t="n"/>
+      <c r="N189" s="4" t="n"/>
+      <c r="O189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -3329,14 +5269,24 @@
           <t>Durex</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr"/>
-      <c r="C190" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="2" t="n"/>
       <c r="D190" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E190" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="n"/>
+      <c r="G190" s="2" t="n"/>
+      <c r="H190" s="2" t="n"/>
+      <c r="I190" s="2" t="n"/>
+      <c r="J190" s="2" t="n"/>
+      <c r="K190" s="2" t="n"/>
+      <c r="L190" s="2" t="n"/>
+      <c r="M190" s="2" t="n"/>
+      <c r="N190" s="2" t="n"/>
+      <c r="O190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -3344,14 +5294,24 @@
           <t>Portable Fan (Small)</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr"/>
-      <c r="C191" s="5" t="n">
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D191" s="5" t="n">
+      <c r="E191" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="E191" s="4" t="inlineStr"/>
+      <c r="F191" s="4" t="n"/>
+      <c r="G191" s="4" t="n"/>
+      <c r="H191" s="4" t="n"/>
+      <c r="I191" s="4" t="n"/>
+      <c r="J191" s="4" t="n"/>
+      <c r="K191" s="4" t="n"/>
+      <c r="L191" s="4" t="n"/>
+      <c r="M191" s="4" t="n"/>
+      <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -3359,14 +5319,24 @@
           <t>Portable Fan (Big)</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr"/>
-      <c r="C192" s="3" t="n">
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D192" s="3" t="n">
+      <c r="E192" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="n"/>
+      <c r="G192" s="2" t="n"/>
+      <c r="H192" s="2" t="n"/>
+      <c r="I192" s="2" t="n"/>
+      <c r="J192" s="2" t="n"/>
+      <c r="K192" s="2" t="n"/>
+      <c r="L192" s="2" t="n"/>
+      <c r="M192" s="2" t="n"/>
+      <c r="N192" s="2" t="n"/>
+      <c r="O192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -3374,14 +5344,24 @@
           <t>Sling Bag - Fluffy Sling</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr"/>
-      <c r="C193" s="5" t="n">
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="D193" s="5" t="n">
+      <c r="E193" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="E193" s="4" t="inlineStr"/>
+      <c r="F193" s="4" t="n"/>
+      <c r="G193" s="4" t="n"/>
+      <c r="H193" s="4" t="n"/>
+      <c r="I193" s="4" t="n"/>
+      <c r="J193" s="4" t="n"/>
+      <c r="K193" s="4" t="n"/>
+      <c r="L193" s="4" t="n"/>
+      <c r="M193" s="4" t="n"/>
+      <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -3389,14 +5369,24 @@
           <t>Sling Bag with a Ribbon</t>
         </is>
       </c>
-      <c r="B194" s="2" t="inlineStr"/>
-      <c r="C194" s="3" t="n">
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="D194" s="3" t="n">
+      <c r="E194" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="2" t="n"/>
+      <c r="H194" s="2" t="n"/>
+      <c r="I194" s="2" t="n"/>
+      <c r="J194" s="2" t="n"/>
+      <c r="K194" s="2" t="n"/>
+      <c r="L194" s="2" t="n"/>
+      <c r="M194" s="2" t="n"/>
+      <c r="N194" s="2" t="n"/>
+      <c r="O194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -3404,14 +5394,24 @@
           <t>Min Min Small Sling Bag</t>
         </is>
       </c>
-      <c r="B195" s="4" t="inlineStr"/>
-      <c r="C195" s="5" t="n">
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="5" t="n">
         <v>550</v>
       </c>
-      <c r="D195" s="5" t="n">
+      <c r="E195" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="E195" s="4" t="inlineStr"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="n"/>
+      <c r="H195" s="4" t="n"/>
+      <c r="I195" s="4" t="n"/>
+      <c r="J195" s="4" t="n"/>
+      <c r="K195" s="4" t="n"/>
+      <c r="L195" s="4" t="n"/>
+      <c r="M195" s="4" t="n"/>
+      <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -3419,14 +5419,24 @@
           <t>2 in 1 Sling Bag (Leather)</t>
         </is>
       </c>
-      <c r="B196" s="2" t="inlineStr"/>
-      <c r="C196" s="3" t="n">
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="D196" s="3" t="n">
+      <c r="E196" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="n"/>
+      <c r="G196" s="2" t="n"/>
+      <c r="H196" s="2" t="n"/>
+      <c r="I196" s="2" t="n"/>
+      <c r="J196" s="2" t="n"/>
+      <c r="K196" s="2" t="n"/>
+      <c r="L196" s="2" t="n"/>
+      <c r="M196" s="2" t="n"/>
+      <c r="N196" s="2" t="n"/>
+      <c r="O196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -3434,14 +5444,24 @@
           <t>Sling Bag (Plain)</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr"/>
-      <c r="C197" s="5" t="n">
+      <c r="B197" s="4" t="n"/>
+      <c r="C197" s="4" t="n"/>
+      <c r="D197" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="D197" s="5" t="n">
+      <c r="E197" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="E197" s="4" t="inlineStr"/>
+      <c r="F197" s="4" t="n"/>
+      <c r="G197" s="4" t="n"/>
+      <c r="H197" s="4" t="n"/>
+      <c r="I197" s="4" t="n"/>
+      <c r="J197" s="4" t="n"/>
+      <c r="K197" s="4" t="n"/>
+      <c r="L197" s="4" t="n"/>
+      <c r="M197" s="4" t="n"/>
+      <c r="N197" s="4" t="n"/>
+      <c r="O197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -3449,14 +5469,24 @@
           <t>Unisex Sling Bag</t>
         </is>
       </c>
-      <c r="B198" s="2" t="inlineStr"/>
-      <c r="C198" s="3" t="n">
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="D198" s="3" t="n">
+      <c r="E198" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="n"/>
+      <c r="G198" s="2" t="n"/>
+      <c r="H198" s="2" t="n"/>
+      <c r="I198" s="2" t="n"/>
+      <c r="J198" s="2" t="n"/>
+      <c r="K198" s="2" t="n"/>
+      <c r="L198" s="2" t="n"/>
+      <c r="M198" s="2" t="n"/>
+      <c r="N198" s="2" t="n"/>
+      <c r="O198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -3464,14 +5494,24 @@
           <t>Waist Bag (Small)</t>
         </is>
       </c>
-      <c r="B199" s="4" t="inlineStr"/>
-      <c r="C199" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="B199" s="4" t="n"/>
+      <c r="C199" s="4" t="n"/>
       <c r="D199" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E199" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="E199" s="4" t="inlineStr"/>
+      <c r="F199" s="4" t="n"/>
+      <c r="G199" s="4" t="n"/>
+      <c r="H199" s="4" t="n"/>
+      <c r="I199" s="4" t="n"/>
+      <c r="J199" s="4" t="n"/>
+      <c r="K199" s="4" t="n"/>
+      <c r="L199" s="4" t="n"/>
+      <c r="M199" s="4" t="n"/>
+      <c r="N199" s="4" t="n"/>
+      <c r="O199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -3479,14 +5519,24 @@
           <t>Waist Bag (Big)</t>
         </is>
       </c>
-      <c r="B200" s="2" t="inlineStr"/>
-      <c r="C200" s="3" t="n">
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D200" s="3" t="n">
+      <c r="E200" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="n"/>
+      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="2" t="n"/>
+      <c r="I200" s="2" t="n"/>
+      <c r="J200" s="2" t="n"/>
+      <c r="K200" s="2" t="n"/>
+      <c r="L200" s="2" t="n"/>
+      <c r="M200" s="2" t="n"/>
+      <c r="N200" s="2" t="n"/>
+      <c r="O200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -3494,14 +5544,24 @@
           <t>Student Tote Bags</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr"/>
-      <c r="C201" s="5" t="n">
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D201" s="5" t="n">
+      <c r="E201" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="E201" s="4" t="inlineStr"/>
+      <c r="F201" s="4" t="n"/>
+      <c r="G201" s="4" t="n"/>
+      <c r="H201" s="4" t="n"/>
+      <c r="I201" s="4" t="n"/>
+      <c r="J201" s="4" t="n"/>
+      <c r="K201" s="4" t="n"/>
+      <c r="L201" s="4" t="n"/>
+      <c r="M201" s="4" t="n"/>
+      <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -3509,14 +5569,24 @@
           <t>Travelling Bags</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr"/>
-      <c r="C202" s="3" t="n">
+      <c r="B202" s="2" t="n"/>
+      <c r="C202" s="2" t="n"/>
+      <c r="D202" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="E202" s="3" t="n">
         <v>1100</v>
       </c>
-      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="n"/>
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="2" t="n"/>
+      <c r="I202" s="2" t="n"/>
+      <c r="J202" s="2" t="n"/>
+      <c r="K202" s="2" t="n"/>
+      <c r="L202" s="2" t="n"/>
+      <c r="M202" s="2" t="n"/>
+      <c r="N202" s="2" t="n"/>
+      <c r="O202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -3524,14 +5594,24 @@
           <t>Dolla Bag</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr"/>
-      <c r="C203" s="5" t="n">
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="4" t="n"/>
+      <c r="D203" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D203" s="5" t="n">
+      <c r="E203" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="E203" s="4" t="inlineStr"/>
+      <c r="F203" s="4" t="n"/>
+      <c r="G203" s="4" t="n"/>
+      <c r="H203" s="4" t="n"/>
+      <c r="I203" s="4" t="n"/>
+      <c r="J203" s="4" t="n"/>
+      <c r="K203" s="4" t="n"/>
+      <c r="L203" s="4" t="n"/>
+      <c r="M203" s="4" t="n"/>
+      <c r="N203" s="4" t="n"/>
+      <c r="O203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -3539,14 +5619,24 @@
           <t>2 in 1 Bag Tote Bag</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr"/>
-      <c r="C204" s="3" t="n">
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="D204" s="3" t="n">
+      <c r="E204" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="n"/>
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="n"/>
+      <c r="I204" s="2" t="n"/>
+      <c r="J204" s="2" t="n"/>
+      <c r="K204" s="2" t="n"/>
+      <c r="L204" s="2" t="n"/>
+      <c r="M204" s="2" t="n"/>
+      <c r="N204" s="2" t="n"/>
+      <c r="O204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -3554,14 +5644,24 @@
           <t>Tote Bag with a Matching Hat</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr"/>
-      <c r="C205" s="5" t="n">
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="5" t="n">
         <v>400</v>
       </c>
-      <c r="D205" s="5" t="n">
+      <c r="E205" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="E205" s="4" t="inlineStr"/>
+      <c r="F205" s="4" t="n"/>
+      <c r="G205" s="4" t="n"/>
+      <c r="H205" s="4" t="n"/>
+      <c r="I205" s="4" t="n"/>
+      <c r="J205" s="4" t="n"/>
+      <c r="K205" s="4" t="n"/>
+      <c r="L205" s="4" t="n"/>
+      <c r="M205" s="4" t="n"/>
+      <c r="N205" s="4" t="n"/>
+      <c r="O205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -3569,14 +5669,24 @@
           <t>Queen Bags</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr"/>
-      <c r="C206" s="3" t="n">
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="2" t="n"/>
+      <c r="D206" s="3" t="n">
         <v>350</v>
       </c>
-      <c r="D206" s="3" t="n">
+      <c r="E206" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="n"/>
+      <c r="G206" s="2" t="n"/>
+      <c r="H206" s="2" t="n"/>
+      <c r="I206" s="2" t="n"/>
+      <c r="J206" s="2" t="n"/>
+      <c r="K206" s="2" t="n"/>
+      <c r="L206" s="2" t="n"/>
+      <c r="M206" s="2" t="n"/>
+      <c r="N206" s="2" t="n"/>
+      <c r="O206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -3584,14 +5694,24 @@
           <t>Straw Bag / Same Bag with a Hat</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr"/>
-      <c r="C207" s="5" t="n">
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="4" t="n"/>
+      <c r="D207" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="D207" s="5" t="n">
+      <c r="E207" s="5" t="n">
         <v>1900</v>
       </c>
-      <c r="E207" s="4" t="inlineStr"/>
+      <c r="F207" s="4" t="n"/>
+      <c r="G207" s="4" t="n"/>
+      <c r="H207" s="4" t="n"/>
+      <c r="I207" s="4" t="n"/>
+      <c r="J207" s="4" t="n"/>
+      <c r="K207" s="4" t="n"/>
+      <c r="L207" s="4" t="n"/>
+      <c r="M207" s="4" t="n"/>
+      <c r="N207" s="4" t="n"/>
+      <c r="O207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -3599,14 +5719,24 @@
           <t>Jute Bag / Woven Bag</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr"/>
-      <c r="C208" s="3" t="n">
+      <c r="B208" s="2" t="n"/>
+      <c r="C208" s="2" t="n"/>
+      <c r="D208" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D208" s="3" t="n">
+      <c r="E208" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="n"/>
+      <c r="G208" s="2" t="n"/>
+      <c r="H208" s="2" t="n"/>
+      <c r="I208" s="2" t="n"/>
+      <c r="J208" s="2" t="n"/>
+      <c r="K208" s="2" t="n"/>
+      <c r="L208" s="2" t="n"/>
+      <c r="M208" s="2" t="n"/>
+      <c r="N208" s="2" t="n"/>
+      <c r="O208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -3614,14 +5744,24 @@
           <t>Partitioned Tote Bags</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr"/>
-      <c r="C209" s="5" t="n">
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="4" t="n"/>
+      <c r="D209" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="D209" s="5" t="n">
+      <c r="E209" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="E209" s="4" t="inlineStr"/>
+      <c r="F209" s="4" t="n"/>
+      <c r="G209" s="4" t="n"/>
+      <c r="H209" s="4" t="n"/>
+      <c r="I209" s="4" t="n"/>
+      <c r="J209" s="4" t="n"/>
+      <c r="K209" s="4" t="n"/>
+      <c r="L209" s="4" t="n"/>
+      <c r="M209" s="4" t="n"/>
+      <c r="N209" s="4" t="n"/>
+      <c r="O209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -3629,14 +5769,24 @@
           <t>Plain Partitioned Bag (Medium)</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr"/>
-      <c r="C210" s="3" t="n">
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="2" t="n"/>
+      <c r="D210" s="3" t="n">
         <v>650</v>
       </c>
-      <c r="D210" s="3" t="n">
+      <c r="E210" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="n"/>
+      <c r="G210" s="2" t="n"/>
+      <c r="H210" s="2" t="n"/>
+      <c r="I210" s="2" t="n"/>
+      <c r="J210" s="2" t="n"/>
+      <c r="K210" s="2" t="n"/>
+      <c r="L210" s="2" t="n"/>
+      <c r="M210" s="2" t="n"/>
+      <c r="N210" s="2" t="n"/>
+      <c r="O210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -3644,14 +5794,24 @@
           <t>Summer Bags (Vibes)</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr"/>
-      <c r="C211" s="5" t="n">
+      <c r="B211" s="4" t="n"/>
+      <c r="C211" s="4" t="n"/>
+      <c r="D211" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="D211" s="5" t="n">
+      <c r="E211" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="E211" s="4" t="inlineStr"/>
+      <c r="F211" s="4" t="n"/>
+      <c r="G211" s="4" t="n"/>
+      <c r="H211" s="4" t="n"/>
+      <c r="I211" s="4" t="n"/>
+      <c r="J211" s="4" t="n"/>
+      <c r="K211" s="4" t="n"/>
+      <c r="L211" s="4" t="n"/>
+      <c r="M211" s="4" t="n"/>
+      <c r="N211" s="4" t="n"/>
+      <c r="O211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -3659,14 +5819,24 @@
           <t>Mothers Bag</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr"/>
-      <c r="C212" s="3" t="n">
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="2" t="n"/>
+      <c r="D212" s="3" t="n">
         <v>1100</v>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="E212" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="n"/>
+      <c r="G212" s="2" t="n"/>
+      <c r="H212" s="2" t="n"/>
+      <c r="I212" s="2" t="n"/>
+      <c r="J212" s="2" t="n"/>
+      <c r="K212" s="2" t="n"/>
+      <c r="L212" s="2" t="n"/>
+      <c r="M212" s="2" t="n"/>
+      <c r="N212" s="2" t="n"/>
+      <c r="O212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -3674,14 +5844,24 @@
           <t>GA Tote Bag</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr"/>
-      <c r="C213" s="5" t="n">
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="D213" s="5" t="n">
+      <c r="E213" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="E213" s="4" t="inlineStr"/>
+      <c r="F213" s="4" t="n"/>
+      <c r="G213" s="4" t="n"/>
+      <c r="H213" s="4" t="n"/>
+      <c r="I213" s="4" t="n"/>
+      <c r="J213" s="4" t="n"/>
+      <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="n"/>
+      <c r="N213" s="4" t="n"/>
+      <c r="O213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -3689,14 +5869,24 @@
           <t>Fendi Tote Bag</t>
         </is>
       </c>
-      <c r="B214" s="2" t="inlineStr"/>
-      <c r="C214" s="3" t="n">
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="D214" s="3" t="n">
+      <c r="E214" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="n"/>
+      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="2" t="n"/>
+      <c r="I214" s="2" t="n"/>
+      <c r="J214" s="2" t="n"/>
+      <c r="K214" s="2" t="n"/>
+      <c r="L214" s="2" t="n"/>
+      <c r="M214" s="2" t="n"/>
+      <c r="N214" s="2" t="n"/>
+      <c r="O214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -3704,14 +5894,24 @@
           <t>Official Bag 2 in 1</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr"/>
-      <c r="C215" s="5" t="n">
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="D215" s="5" t="n">
+      <c r="E215" s="5" t="n">
         <v>1900</v>
       </c>
-      <c r="E215" s="4" t="inlineStr"/>
+      <c r="F215" s="4" t="n"/>
+      <c r="G215" s="4" t="n"/>
+      <c r="H215" s="4" t="n"/>
+      <c r="I215" s="4" t="n"/>
+      <c r="J215" s="4" t="n"/>
+      <c r="K215" s="4" t="n"/>
+      <c r="L215" s="4" t="n"/>
+      <c r="M215" s="4" t="n"/>
+      <c r="N215" s="4" t="n"/>
+      <c r="O215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -3719,14 +5919,24 @@
           <t>Minmin Bag Medium (Original)</t>
         </is>
       </c>
-      <c r="B216" s="2" t="inlineStr"/>
-      <c r="C216" s="3" t="n">
+      <c r="B216" s="2" t="n"/>
+      <c r="C216" s="2" t="n"/>
+      <c r="D216" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="D216" s="3" t="n">
+      <c r="E216" s="3" t="n">
         <v>1900</v>
       </c>
-      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="n"/>
+      <c r="G216" s="2" t="n"/>
+      <c r="H216" s="2" t="n"/>
+      <c r="I216" s="2" t="n"/>
+      <c r="J216" s="2" t="n"/>
+      <c r="K216" s="2" t="n"/>
+      <c r="L216" s="2" t="n"/>
+      <c r="M216" s="2" t="n"/>
+      <c r="N216" s="2" t="n"/>
+      <c r="O216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -3734,14 +5944,24 @@
           <t>Coach Leather Bag</t>
         </is>
       </c>
-      <c r="B217" s="4" t="inlineStr"/>
-      <c r="C217" s="5" t="n">
+      <c r="B217" s="4" t="n"/>
+      <c r="C217" s="4" t="n"/>
+      <c r="D217" s="5" t="n">
         <v>1100</v>
       </c>
-      <c r="D217" s="5" t="n">
+      <c r="E217" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="E217" s="4" t="inlineStr"/>
+      <c r="F217" s="4" t="n"/>
+      <c r="G217" s="4" t="n"/>
+      <c r="H217" s="4" t="n"/>
+      <c r="I217" s="4" t="n"/>
+      <c r="J217" s="4" t="n"/>
+      <c r="K217" s="4" t="n"/>
+      <c r="L217" s="4" t="n"/>
+      <c r="M217" s="4" t="n"/>
+      <c r="N217" s="4" t="n"/>
+      <c r="O217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -3749,14 +5969,24 @@
           <t>Burberry Bag</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr"/>
-      <c r="C218" s="3" t="n">
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="2" t="n"/>
+      <c r="D218" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="D218" s="3" t="n">
+      <c r="E218" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="n"/>
+      <c r="G218" s="2" t="n"/>
+      <c r="H218" s="2" t="n"/>
+      <c r="I218" s="2" t="n"/>
+      <c r="J218" s="2" t="n"/>
+      <c r="K218" s="2" t="n"/>
+      <c r="L218" s="2" t="n"/>
+      <c r="M218" s="2" t="n"/>
+      <c r="N218" s="2" t="n"/>
+      <c r="O218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -3764,14 +5994,24 @@
           <t>Chain Tote Bag</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr"/>
-      <c r="C219" s="5" t="n">
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="4" t="n"/>
+      <c r="D219" s="5" t="n">
         <v>750</v>
       </c>
-      <c r="D219" s="5" t="n">
+      <c r="E219" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="E219" s="4" t="inlineStr"/>
+      <c r="F219" s="4" t="n"/>
+      <c r="G219" s="4" t="n"/>
+      <c r="H219" s="4" t="n"/>
+      <c r="I219" s="4" t="n"/>
+      <c r="J219" s="4" t="n"/>
+      <c r="K219" s="4" t="n"/>
+      <c r="L219" s="4" t="n"/>
+      <c r="M219" s="4" t="n"/>
+      <c r="N219" s="4" t="n"/>
+      <c r="O219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -3779,14 +6019,24 @@
           <t>3 in 1 Official Bag</t>
         </is>
       </c>
-      <c r="B220" s="2" t="inlineStr"/>
-      <c r="C220" s="3" t="n">
+      <c r="B220" s="2" t="n"/>
+      <c r="C220" s="2" t="n"/>
+      <c r="D220" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="D220" s="3" t="n">
+      <c r="E220" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="n"/>
+      <c r="G220" s="2" t="n"/>
+      <c r="H220" s="2" t="n"/>
+      <c r="I220" s="2" t="n"/>
+      <c r="J220" s="2" t="n"/>
+      <c r="K220" s="2" t="n"/>
+      <c r="L220" s="2" t="n"/>
+      <c r="M220" s="2" t="n"/>
+      <c r="N220" s="2" t="n"/>
+      <c r="O220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -3794,14 +6044,24 @@
           <t>5 in 1 Bags</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr"/>
-      <c r="C221" s="5" t="n">
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="4" t="n"/>
+      <c r="D221" s="5" t="n">
         <v>1800</v>
       </c>
-      <c r="D221" s="5" t="n">
+      <c r="E221" s="5" t="n">
         <v>3500</v>
       </c>
-      <c r="E221" s="4" t="inlineStr"/>
+      <c r="F221" s="4" t="n"/>
+      <c r="G221" s="4" t="n"/>
+      <c r="H221" s="4" t="n"/>
+      <c r="I221" s="4" t="n"/>
+      <c r="J221" s="4" t="n"/>
+      <c r="K221" s="4" t="n"/>
+      <c r="L221" s="4" t="n"/>
+      <c r="M221" s="4" t="n"/>
+      <c r="N221" s="4" t="n"/>
+      <c r="O221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -3809,14 +6069,24 @@
           <t>4 in 1 Bags</t>
         </is>
       </c>
-      <c r="B222" s="2" t="inlineStr"/>
-      <c r="C222" s="3" t="n">
+      <c r="B222" s="2" t="n"/>
+      <c r="C222" s="2" t="n"/>
+      <c r="D222" s="3" t="n">
         <v>1700</v>
       </c>
-      <c r="D222" s="3" t="n">
+      <c r="E222" s="3" t="n">
         <v>3500</v>
       </c>
-      <c r="E222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="n"/>
+      <c r="G222" s="2" t="n"/>
+      <c r="H222" s="2" t="n"/>
+      <c r="I222" s="2" t="n"/>
+      <c r="J222" s="2" t="n"/>
+      <c r="K222" s="2" t="n"/>
+      <c r="L222" s="2" t="n"/>
+      <c r="M222" s="2" t="n"/>
+      <c r="N222" s="2" t="n"/>
+      <c r="O222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -3824,14 +6094,24 @@
           <t>Monkey Bag Flowered</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr"/>
-      <c r="C223" s="5" t="n">
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="4" t="n"/>
+      <c r="D223" s="5" t="n">
         <v>650</v>
       </c>
-      <c r="D223" s="5" t="n">
+      <c r="E223" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="E223" s="4" t="inlineStr"/>
+      <c r="F223" s="4" t="n"/>
+      <c r="G223" s="4" t="n"/>
+      <c r="H223" s="4" t="n"/>
+      <c r="I223" s="4" t="n"/>
+      <c r="J223" s="4" t="n"/>
+      <c r="K223" s="4" t="n"/>
+      <c r="L223" s="4" t="n"/>
+      <c r="M223" s="4" t="n"/>
+      <c r="N223" s="4" t="n"/>
+      <c r="O223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -3839,14 +6119,24 @@
           <t>Monkey Bag Plain</t>
         </is>
       </c>
-      <c r="B224" s="2" t="inlineStr"/>
-      <c r="C224" s="3" t="n">
+      <c r="B224" s="2" t="n"/>
+      <c r="C224" s="2" t="n"/>
+      <c r="D224" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="E224" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="n"/>
+      <c r="G224" s="2" t="n"/>
+      <c r="H224" s="2" t="n"/>
+      <c r="I224" s="2" t="n"/>
+      <c r="J224" s="2" t="n"/>
+      <c r="K224" s="2" t="n"/>
+      <c r="L224" s="2" t="n"/>
+      <c r="M224" s="2" t="n"/>
+      <c r="N224" s="2" t="n"/>
+      <c r="O224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -3854,14 +6144,24 @@
           <t>Minmin Big Bag</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr"/>
-      <c r="C225" s="5" t="n">
+      <c r="B225" s="4" t="n"/>
+      <c r="C225" s="4" t="n"/>
+      <c r="D225" s="5" t="n">
         <v>700</v>
       </c>
-      <c r="D225" s="5" t="n">
+      <c r="E225" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="E225" s="4" t="inlineStr"/>
+      <c r="F225" s="4" t="n"/>
+      <c r="G225" s="4" t="n"/>
+      <c r="H225" s="4" t="n"/>
+      <c r="I225" s="4" t="n"/>
+      <c r="J225" s="4" t="n"/>
+      <c r="K225" s="4" t="n"/>
+      <c r="L225" s="4" t="n"/>
+      <c r="M225" s="4" t="n"/>
+      <c r="N225" s="4" t="n"/>
+      <c r="O225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -3869,14 +6169,24 @@
           <t>Cellophone Bag</t>
         </is>
       </c>
-      <c r="B226" s="2" t="inlineStr"/>
-      <c r="C226" s="3" t="n">
+      <c r="B226" s="2" t="n"/>
+      <c r="C226" s="2" t="n"/>
+      <c r="D226" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="D226" s="3" t="n">
+      <c r="E226" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="n"/>
+      <c r="G226" s="2" t="n"/>
+      <c r="H226" s="2" t="n"/>
+      <c r="I226" s="2" t="n"/>
+      <c r="J226" s="2" t="n"/>
+      <c r="K226" s="2" t="n"/>
+      <c r="L226" s="2" t="n"/>
+      <c r="M226" s="2" t="n"/>
+      <c r="N226" s="2" t="n"/>
+      <c r="O226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -3884,17 +6194,27 @@
           <t>Cello Phone Bag (Small)</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr"/>
-      <c r="C227" s="5" t="n">
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D227" s="5" t="n">
+      <c r="E227" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="E227" s="4" t="inlineStr"/>
+      <c r="F227" s="4" t="n"/>
+      <c r="G227" s="4" t="n"/>
+      <c r="H227" s="4" t="n"/>
+      <c r="I227" s="4" t="n"/>
+      <c r="J227" s="4" t="n"/>
+      <c r="K227" s="4" t="n"/>
+      <c r="L227" s="4" t="n"/>
+      <c r="M227" s="4" t="n"/>
+      <c r="N227" s="4" t="n"/>
+      <c r="O227" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E227"/>
+  <autoFilter ref="A1:O227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>